--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="439">
   <si>
     <t>Area</t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>Mr. S.MEDHANI CHAMINDIKA</t>
+  </si>
+  <si>
+    <t>STATUS PENDING</t>
   </si>
   <si>
     <t>WAYAMBA</t>
@@ -1340,10 +1343,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1392,16 +1395,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1415,22 +1418,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1444,14 +1434,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1459,7 +1441,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -1484,14 +1465,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
@@ -1501,14 +1474,28 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1522,8 +1509,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1544,7 +1547,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1556,7 +1577,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1568,13 +1601,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1586,31 +1691,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1622,49 +1709,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1676,49 +1721,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1753,24 +1756,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1782,6 +1767,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1801,6 +1795,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1812,26 +1824,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1850,18 +1842,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1873,106 +1876,106 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1981,22 +1984,22 @@
     <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3771,16 +3774,22 @@
       <c r="P22" s="17">
         <v>495000</v>
       </c>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
+      <c r="Q22" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R22" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S22" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T22" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -3792,19 +3801,19 @@
         <v>89</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J23" s="14">
         <v>46053</v>
@@ -3830,39 +3839,43 @@
       <c r="Q23" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
+      <c r="R23" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S23" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T23" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J24" s="14">
         <v>46108</v>
@@ -3885,40 +3898,46 @@
       <c r="P24" s="17">
         <v>495000</v>
       </c>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
+      <c r="Q24" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R24" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T24" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J25" s="14">
         <v>46112</v>
@@ -3941,8 +3960,12 @@
       <c r="P25" s="17">
         <v>495000</v>
       </c>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
+      <c r="Q25" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="S25" s="19" t="s">
         <v>94</v>
       </c>
@@ -3952,7 +3975,7 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>130</v>
@@ -3964,19 +3987,19 @@
         <v>132</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J26" s="14">
         <v>46106</v>
@@ -4014,31 +4037,31 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J27" s="14">
         <v>46109</v>
@@ -4061,8 +4084,12 @@
       <c r="P27" s="17">
         <v>495000</v>
       </c>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
+      <c r="Q27" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R27" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="S27" s="19" t="s">
         <v>94</v>
       </c>
@@ -4072,31 +4099,31 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J28" s="14">
         <v>46109</v>
@@ -4119,16 +4146,22 @@
       <c r="P28" s="17">
         <v>247500</v>
       </c>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
+      <c r="Q28" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R28" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S28" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T28" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>33</v>
@@ -4140,19 +4173,19 @@
         <v>35</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J29" s="14">
         <v>46109</v>
@@ -4190,31 +4223,31 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J30" s="14">
         <v>46111</v>
@@ -4237,31 +4270,37 @@
       <c r="P30" s="17">
         <v>550000</v>
       </c>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
+      <c r="Q30" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R30" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S30" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T30" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>25</v>
@@ -4270,7 +4309,7 @@
         <v>7701603390</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J31" s="14">
         <v>46111</v>
@@ -4293,8 +4332,12 @@
       <c r="P31" s="17">
         <v>245000</v>
       </c>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
+      <c r="Q31" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R31" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="S31" s="19" t="s">
         <v>94</v>
       </c>
@@ -4304,31 +4347,31 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J32" s="14">
         <v>46111</v>
@@ -4351,8 +4394,12 @@
       <c r="P32" s="17">
         <v>247500</v>
       </c>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
+      <c r="Q32" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R32" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="S32" s="19" t="s">
         <v>94</v>
       </c>
@@ -4362,31 +4409,31 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J33" s="14">
         <v>46111</v>
@@ -4409,31 +4456,37 @@
       <c r="P33" s="17">
         <v>247500</v>
       </c>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
+      <c r="Q33" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R33" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S33" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T33" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>25</v>
@@ -4442,7 +4495,7 @@
         <v>70602147</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J34" s="14">
         <v>46111</v>
@@ -4465,31 +4518,37 @@
       <c r="P34" s="17">
         <v>245000</v>
       </c>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
+      <c r="Q34" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R34" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S34" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T34" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>25</v>
@@ -4498,7 +4557,7 @@
         <v>515701970</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J35" s="14">
         <v>46111</v>
@@ -4521,40 +4580,46 @@
       <c r="P35" s="17">
         <v>275000</v>
       </c>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
+      <c r="Q35" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R35" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S35" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T35" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J36" s="14">
         <v>46111</v>
@@ -4577,40 +4642,46 @@
       <c r="P36" s="17">
         <v>275000</v>
       </c>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
+      <c r="Q36" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R36" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S36" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T36" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J37" s="14">
         <v>46112</v>
@@ -4633,8 +4704,12 @@
       <c r="P37" s="17">
         <v>550000</v>
       </c>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
+      <c r="Q37" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R37" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="S37" s="19" t="s">
         <v>94</v>
       </c>
@@ -4644,31 +4719,31 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J38" s="14">
         <v>46112</v>
@@ -4691,8 +4766,12 @@
       <c r="P38" s="17">
         <v>475000</v>
       </c>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
+      <c r="Q38" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R38" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="S38" s="19" t="s">
         <v>94</v>
       </c>
@@ -4708,25 +4787,25 @@
         <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J39" s="14">
         <v>46112</v>
@@ -4749,31 +4828,37 @@
       <c r="P39" s="17">
         <v>375000</v>
       </c>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
+      <c r="Q39" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R39" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S39" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T39" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>25</v>
@@ -4782,7 +4867,7 @@
         <v>679004406</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J40" s="14">
         <v>46112</v>
@@ -4805,40 +4890,46 @@
       <c r="P40" s="17">
         <v>475000</v>
       </c>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
+      <c r="Q40" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R40" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S40" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T40" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J41" s="14">
         <v>46112</v>
@@ -4861,8 +4952,12 @@
       <c r="P41" s="17">
         <v>325000</v>
       </c>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
+      <c r="Q41" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R41" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="S41" s="19" t="s">
         <v>94</v>
       </c>
@@ -4872,31 +4967,31 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J42" s="14">
         <v>46112</v>
@@ -4919,31 +5014,37 @@
       <c r="P42" s="17">
         <v>375000</v>
       </c>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
-      <c r="S42" s="19"/>
+      <c r="Q42" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R42" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S42" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T42" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>25</v>
@@ -4952,7 +5053,7 @@
         <v>6478802340</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J43" s="14">
         <v>46112</v>
@@ -4979,7 +5080,7 @@
         <v>28</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S43" s="19" t="s">
         <v>94</v>
@@ -4990,31 +5091,31 @@
     </row>
     <row r="44" spans="1:20">
       <c r="A44" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J44" s="14">
         <v>46112</v>
@@ -5037,9 +5138,15 @@
       <c r="P44" s="17">
         <v>475000</v>
       </c>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="19"/>
-      <c r="S44" s="19"/>
+      <c r="Q44" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R44" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S44" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T44" s="19" t="s">
         <v>43</v>
       </c>
@@ -5052,16 +5159,16 @@
         <v>70</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>25</v>
@@ -5070,7 +5177,7 @@
         <v>106804280</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J45" s="14">
         <v>46112</v>
@@ -5093,31 +5200,37 @@
       <c r="P45" s="17">
         <v>550000</v>
       </c>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="19"/>
-      <c r="S45" s="19"/>
+      <c r="Q45" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R45" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S45" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T45" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>25</v>
@@ -5126,7 +5239,7 @@
         <v>5012804793</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J46" s="14">
         <v>46142</v>
@@ -5149,31 +5262,37 @@
       <c r="P46" s="17">
         <v>475000</v>
       </c>
-      <c r="Q46" s="19"/>
-      <c r="R46" s="19"/>
-      <c r="S46" s="19"/>
+      <c r="Q46" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R46" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S46" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T46" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>25</v>
@@ -5182,7 +5301,7 @@
         <v>8986603515</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J47" s="14">
         <v>46112</v>
@@ -5205,16 +5324,22 @@
       <c r="P47" s="17">
         <v>550000</v>
       </c>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="19"/>
+      <c r="Q47" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R47" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S47" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T47" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>33</v>
@@ -5226,19 +5351,19 @@
         <v>126</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J48" s="14">
         <v>46112</v>
@@ -5261,40 +5386,46 @@
       <c r="P48" s="17">
         <v>550000</v>
       </c>
-      <c r="Q48" s="19"/>
-      <c r="R48" s="19"/>
-      <c r="S48" s="19"/>
+      <c r="Q48" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R48" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S48" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T48" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J49" s="14">
         <v>46142</v>
@@ -5317,16 +5448,22 @@
       <c r="P49" s="17">
         <v>550000</v>
       </c>
-      <c r="Q49" s="19"/>
-      <c r="R49" s="19"/>
-      <c r="S49" s="19"/>
+      <c r="Q49" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R49" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S49" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T49" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:20">
       <c r="A50" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>20</v>
@@ -5338,19 +5475,19 @@
         <v>22</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J50" s="14">
         <v>46099</v>
@@ -5373,16 +5510,22 @@
       <c r="P50" s="17">
         <v>245000</v>
       </c>
-      <c r="Q50" s="19"/>
-      <c r="R50" s="19"/>
-      <c r="S50" s="19"/>
+      <c r="Q50" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R50" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S50" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T50" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>20</v>
@@ -5394,10 +5537,10 @@
         <v>22</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>25</v>
@@ -5406,7 +5549,7 @@
         <v>6801200161</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J51" s="14">
         <v>46100</v>
@@ -5429,31 +5572,37 @@
       <c r="P51" s="17">
         <v>300000</v>
       </c>
-      <c r="Q51" s="19"/>
-      <c r="R51" s="19"/>
-      <c r="S51" s="19"/>
+      <c r="Q51" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R51" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S51" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T51" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>119</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>25</v>
@@ -5462,7 +5611,7 @@
         <v>7931304541</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J52" s="14">
         <v>46109</v>
@@ -5500,31 +5649,31 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J53" s="14">
         <v>46111</v>
@@ -5562,22 +5711,22 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>25</v>
@@ -5586,7 +5735,7 @@
         <v>419502402</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J54" s="14">
         <v>46142</v>
@@ -5609,40 +5758,46 @@
       <c r="P54" s="17">
         <v>375000</v>
       </c>
-      <c r="Q54" s="19"/>
-      <c r="R54" s="19"/>
-      <c r="S54" s="19"/>
+      <c r="Q54" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R54" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S54" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T54" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J55" s="14">
         <v>46112</v>
@@ -5665,31 +5820,37 @@
       <c r="P55" s="17">
         <v>475000</v>
       </c>
-      <c r="Q55" s="19"/>
-      <c r="R55" s="19"/>
-      <c r="S55" s="19"/>
+      <c r="Q55" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R55" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S55" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T55" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>25</v>
@@ -5698,7 +5859,7 @@
         <v>114404305</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J56" s="14">
         <v>46112</v>
@@ -5721,40 +5882,46 @@
       <c r="P56" s="17">
         <v>495000</v>
       </c>
-      <c r="Q56" s="19"/>
-      <c r="R56" s="19"/>
-      <c r="S56" s="19"/>
+      <c r="Q56" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R56" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S56" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T56" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J57" s="14">
         <v>46112</v>
@@ -5777,40 +5944,46 @@
       <c r="P57" s="17">
         <v>550000</v>
       </c>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="19"/>
-      <c r="S57" s="19"/>
+      <c r="Q57" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R57" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S57" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T57" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J58" s="14">
         <v>46142</v>
@@ -5848,31 +6021,31 @@
     </row>
     <row r="59" spans="1:20">
       <c r="A59" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J59" s="14">
         <v>46142</v>
@@ -5901,14 +6074,16 @@
       <c r="R59" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="S59" s="19"/>
+      <c r="S59" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T59" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>119</v>
@@ -5920,10 +6095,10 @@
         <v>121</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>25</v>
@@ -5932,7 +6107,7 @@
         <v>661101038</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J60" s="14">
         <v>46112</v>
@@ -5955,40 +6130,46 @@
       <c r="P60" s="17">
         <v>495000</v>
       </c>
-      <c r="Q60" s="19"/>
-      <c r="R60" s="19"/>
-      <c r="S60" s="19"/>
+      <c r="Q60" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R60" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S60" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T60" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J61" s="14">
         <v>46112</v>
@@ -6026,31 +6207,31 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J62" s="14">
         <v>46112</v>
@@ -6088,7 +6269,7 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>20</v>
@@ -6100,10 +6281,10 @@
         <v>22</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>25</v>
@@ -6112,7 +6293,7 @@
         <v>8915001242</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J63" s="14">
         <v>46112</v>
@@ -6135,16 +6316,22 @@
       <c r="P63" s="17">
         <v>235000</v>
       </c>
-      <c r="Q63" s="19"/>
-      <c r="R63" s="19"/>
-      <c r="S63" s="19"/>
+      <c r="Q63" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R63" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S63" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T63" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>20</v>
@@ -6156,10 +6343,10 @@
         <v>22</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>25</v>
@@ -6168,7 +6355,7 @@
         <v>162600148</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J64" s="14">
         <v>46112</v>
@@ -6212,16 +6399,16 @@
         <v>151</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>25</v>
@@ -6230,7 +6417,7 @@
         <v>162303825</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J65" s="14">
         <v>46173</v>
@@ -6280,19 +6467,19 @@
         <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J66" s="14">
         <v>46148</v>
@@ -6315,16 +6502,22 @@
       <c r="P66" s="17">
         <v>550000</v>
       </c>
-      <c r="Q66" s="19"/>
-      <c r="R66" s="19"/>
-      <c r="S66" s="19"/>
+      <c r="Q66" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R66" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S66" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T66" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>20</v>
@@ -6336,10 +6529,10 @@
         <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>25</v>
@@ -6348,7 +6541,7 @@
         <v>8005902216</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J67" s="14">
         <v>46150</v>
@@ -6398,10 +6591,10 @@
         <v>79</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>25</v>
@@ -6410,7 +6603,7 @@
         <v>7157401261</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J68" s="14">
         <v>46184</v>
@@ -6433,40 +6626,46 @@
       <c r="P68" s="17">
         <v>475000</v>
       </c>
-      <c r="Q68" s="19"/>
-      <c r="R68" s="19"/>
-      <c r="S68" s="19"/>
+      <c r="Q68" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R68" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S68" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T68" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:20">
       <c r="A69" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J69" s="14">
         <v>46203</v>
@@ -6504,7 +6703,7 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>20</v>
@@ -6516,19 +6715,19 @@
         <v>22</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J70" s="14">
         <v>46196</v>
@@ -6551,16 +6750,22 @@
       <c r="P70" s="17">
         <v>475000</v>
       </c>
-      <c r="Q70" s="19"/>
-      <c r="R70" s="19"/>
-      <c r="S70" s="19"/>
+      <c r="Q70" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R70" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S70" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T70" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:20">
       <c r="A71" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>20</v>
@@ -6572,19 +6777,19 @@
         <v>22</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J71" s="14">
         <v>46196</v>
@@ -6607,16 +6812,22 @@
       <c r="P71" s="17">
         <v>220000</v>
       </c>
-      <c r="Q71" s="19"/>
-      <c r="R71" s="19"/>
-      <c r="S71" s="19"/>
+      <c r="Q71" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R71" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S71" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T71" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:20">
       <c r="A72" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>20</v>
@@ -6628,10 +6839,10 @@
         <v>22</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>25</v>
@@ -6640,7 +6851,7 @@
         <v>203402736</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J72" s="14">
         <v>46197</v>
@@ -6663,9 +6874,15 @@
       <c r="P72" s="17">
         <v>220000</v>
       </c>
-      <c r="Q72" s="19"/>
-      <c r="R72" s="19"/>
-      <c r="S72" s="19"/>
+      <c r="Q72" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R72" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S72" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T72" s="19" t="s">
         <v>43</v>
       </c>
@@ -6675,28 +6892,28 @@
         <v>150</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J73" s="14">
         <v>46203</v>
@@ -6719,16 +6936,22 @@
       <c r="P73" s="17">
         <v>475000</v>
       </c>
-      <c r="Q73" s="19"/>
-      <c r="R73" s="19"/>
-      <c r="S73" s="19"/>
+      <c r="Q73" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R73" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S73" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T73" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:20">
       <c r="A74" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>20</v>
@@ -6740,19 +6963,19 @@
         <v>22</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J74" s="14">
         <v>46173</v>
@@ -6775,16 +6998,22 @@
       <c r="P74" s="17">
         <v>125000</v>
       </c>
-      <c r="Q74" s="19"/>
-      <c r="R74" s="19"/>
-      <c r="S74" s="19"/>
+      <c r="Q74" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R74" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S74" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T74" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:20">
       <c r="A75" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>20</v>
@@ -6796,19 +7025,19 @@
         <v>22</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J75" s="14">
         <v>46173</v>
@@ -6831,16 +7060,22 @@
       <c r="P75" s="17">
         <v>237500</v>
       </c>
-      <c r="Q75" s="19"/>
-      <c r="R75" s="19"/>
-      <c r="S75" s="19"/>
+      <c r="Q75" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R75" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S75" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T75" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>20</v>
@@ -6852,19 +7087,19 @@
         <v>22</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J76" s="14">
         <v>46173</v>
@@ -6887,16 +7122,22 @@
       <c r="P76" s="17">
         <v>247500</v>
       </c>
-      <c r="Q76" s="19"/>
-      <c r="R76" s="19"/>
-      <c r="S76" s="19"/>
+      <c r="Q76" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R76" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S76" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T76" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:20">
       <c r="A77" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>20</v>
@@ -6908,19 +7149,19 @@
         <v>22</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J77" s="14">
         <v>46173</v>
@@ -6943,16 +7184,22 @@
       <c r="P77" s="17">
         <v>245000</v>
       </c>
-      <c r="Q77" s="19"/>
-      <c r="R77" s="19"/>
-      <c r="S77" s="19"/>
+      <c r="Q77" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R77" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S77" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T77" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:20">
       <c r="A78" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>20</v>
@@ -6964,19 +7211,19 @@
         <v>22</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J78" s="14">
         <v>46173</v>
@@ -6999,16 +7246,22 @@
       <c r="P78" s="17">
         <v>205000</v>
       </c>
-      <c r="Q78" s="19"/>
-      <c r="R78" s="19"/>
-      <c r="S78" s="19"/>
+      <c r="Q78" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R78" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S78" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T78" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>20</v>
@@ -7020,19 +7273,19 @@
         <v>22</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J79" s="14">
         <v>46173</v>
@@ -7055,16 +7308,22 @@
       <c r="P79" s="17">
         <v>230000</v>
       </c>
-      <c r="Q79" s="19"/>
-      <c r="R79" s="19"/>
-      <c r="S79" s="19"/>
+      <c r="Q79" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R79" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S79" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="T79" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>20</v>
@@ -7076,19 +7335,19 @@
         <v>22</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J80" s="14">
         <v>46203</v>

--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="440">
   <si>
     <t>Area</t>
   </si>
@@ -732,6 +732,9 @@
   </si>
   <si>
     <t>Mrs. SUVINEETHA</t>
+  </si>
+  <si>
+    <t>CR RECEIVED TO SLMO</t>
   </si>
   <si>
     <t>COLOMBO METRO</t>
@@ -1342,10 +1345,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="25">
@@ -1389,7 +1392,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1400,6 +1403,53 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1418,47 +1468,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1472,6 +1483,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -1481,7 +1499,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1495,23 +1521,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1520,13 +1530,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1547,7 +1550,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1559,7 +1562,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1571,19 +1586,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1595,19 +1670,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1625,109 +1730,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1771,15 +1774,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1798,17 +1792,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1828,6 +1824,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1842,29 +1856,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1879,127 +1882,127 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2401,10 +2404,10 @@
   <dimension ref="A1:T80"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.0909090909091" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="26.0909090909091" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3636363636364" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="15.9090909090909" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="15.0909090909091" customWidth="1"/>
+    <col min="2" max="2" width="26.0909090909091" customWidth="1"/>
+    <col min="3" max="3" width="11.3636363636364" customWidth="1"/>
+    <col min="4" max="4" width="15.9090909090909" customWidth="1"/>
     <col min="5" max="5" width="12.6363636363636" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="8.27272727272727" customWidth="1"/>
@@ -4705,13 +4708,13 @@
         <v>550000</v>
       </c>
       <c r="Q37" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R37" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S37" s="19" t="s">
-        <v>94</v>
+        <v>238</v>
       </c>
       <c r="T37" s="19" t="s">
         <v>43</v>
@@ -4719,31 +4722,31 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J38" s="14">
         <v>46112</v>
@@ -4787,25 +4790,25 @@
         <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J39" s="14">
         <v>46112</v>
@@ -4849,16 +4852,16 @@
         <v>203</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>25</v>
@@ -4867,7 +4870,7 @@
         <v>679004406</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J40" s="14">
         <v>46112</v>
@@ -4917,19 +4920,19 @@
         <v>192</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J41" s="14">
         <v>46112</v>
@@ -4979,19 +4982,19 @@
         <v>192</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J42" s="14">
         <v>46112</v>
@@ -5041,10 +5044,10 @@
         <v>192</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>25</v>
@@ -5053,7 +5056,7 @@
         <v>6478802340</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J43" s="14">
         <v>46112</v>
@@ -5080,7 +5083,7 @@
         <v>28</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S43" s="19" t="s">
         <v>94</v>
@@ -5094,28 +5097,28 @@
         <v>183</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J44" s="14">
         <v>46112</v>
@@ -5159,16 +5162,16 @@
         <v>70</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>25</v>
@@ -5177,7 +5180,7 @@
         <v>106804280</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J45" s="14">
         <v>46112</v>
@@ -5215,22 +5218,22 @@
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>25</v>
@@ -5239,7 +5242,7 @@
         <v>5012804793</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J46" s="14">
         <v>46142</v>
@@ -5283,16 +5286,16 @@
         <v>33</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>25</v>
@@ -5301,7 +5304,7 @@
         <v>8986603515</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J47" s="14">
         <v>46112</v>
@@ -5351,19 +5354,19 @@
         <v>126</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J48" s="14">
         <v>46112</v>
@@ -5413,19 +5416,19 @@
         <v>174</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J49" s="14">
         <v>46142</v>
@@ -5475,19 +5478,19 @@
         <v>22</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J50" s="14">
         <v>46099</v>
@@ -5537,10 +5540,10 @@
         <v>22</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>25</v>
@@ -5549,7 +5552,7 @@
         <v>6801200161</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J51" s="14">
         <v>46100</v>
@@ -5593,16 +5596,16 @@
         <v>119</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>25</v>
@@ -5611,7 +5614,7 @@
         <v>7931304541</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J52" s="14">
         <v>46109</v>
@@ -5655,25 +5658,25 @@
         <v>49</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J53" s="14">
         <v>46111</v>
@@ -5714,19 +5717,19 @@
         <v>183</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>25</v>
@@ -5735,7 +5738,7 @@
         <v>419502402</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J54" s="14">
         <v>46142</v>
@@ -5773,31 +5776,31 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J55" s="14">
         <v>46112</v>
@@ -5835,22 +5838,22 @@
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>25</v>
@@ -5859,7 +5862,7 @@
         <v>114404305</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J56" s="14">
         <v>46112</v>
@@ -5897,31 +5900,31 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J57" s="14">
         <v>46112</v>
@@ -5965,25 +5968,25 @@
         <v>33</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J58" s="14">
         <v>46142</v>
@@ -6027,25 +6030,25 @@
         <v>33</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J59" s="14">
         <v>46142</v>
@@ -6095,10 +6098,10 @@
         <v>121</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>25</v>
@@ -6107,7 +6110,7 @@
         <v>661101038</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J60" s="14">
         <v>46112</v>
@@ -6151,25 +6154,25 @@
         <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J61" s="14">
         <v>46112</v>
@@ -6213,25 +6216,25 @@
         <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J62" s="14">
         <v>46112</v>
@@ -6281,10 +6284,10 @@
         <v>22</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>25</v>
@@ -6293,7 +6296,7 @@
         <v>8915001242</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J63" s="14">
         <v>46112</v>
@@ -6343,10 +6346,10 @@
         <v>22</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>25</v>
@@ -6355,7 +6358,7 @@
         <v>162600148</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J64" s="14">
         <v>46112</v>
@@ -6399,16 +6402,16 @@
         <v>151</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>25</v>
@@ -6417,7 +6420,7 @@
         <v>162303825</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J65" s="14">
         <v>46173</v>
@@ -6467,19 +6470,19 @@
         <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J66" s="14">
         <v>46148</v>
@@ -6529,10 +6532,10 @@
         <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>25</v>
@@ -6541,7 +6544,7 @@
         <v>8005902216</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J67" s="14">
         <v>46150</v>
@@ -6591,10 +6594,10 @@
         <v>79</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>25</v>
@@ -6603,7 +6606,7 @@
         <v>7157401261</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J68" s="14">
         <v>46184</v>
@@ -6627,10 +6630,10 @@
         <v>475000</v>
       </c>
       <c r="Q68" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R68" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S68" s="19" t="s">
         <v>158</v>
@@ -6641,31 +6644,31 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J69" s="14">
         <v>46203</v>
@@ -6715,19 +6718,19 @@
         <v>22</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J70" s="14">
         <v>46196</v>
@@ -6751,13 +6754,13 @@
         <v>475000</v>
       </c>
       <c r="Q70" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R70" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S70" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T70" s="19" t="s">
         <v>43</v>
@@ -6777,19 +6780,19 @@
         <v>22</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J71" s="14">
         <v>46196</v>
@@ -6813,13 +6816,13 @@
         <v>220000</v>
       </c>
       <c r="Q71" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R71" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S71" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T71" s="19" t="s">
         <v>43</v>
@@ -6839,10 +6842,10 @@
         <v>22</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>25</v>
@@ -6851,7 +6854,7 @@
         <v>203402736</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J72" s="14">
         <v>46197</v>
@@ -6875,13 +6878,13 @@
         <v>220000</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R72" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S72" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T72" s="19" t="s">
         <v>43</v>
@@ -6892,28 +6895,28 @@
         <v>150</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J73" s="14">
         <v>46203</v>
@@ -6963,19 +6966,19 @@
         <v>22</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J74" s="14">
         <v>46173</v>
@@ -6999,13 +7002,13 @@
         <v>125000</v>
       </c>
       <c r="Q74" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R74" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S74" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T74" s="19" t="s">
         <v>43</v>
@@ -7025,19 +7028,19 @@
         <v>22</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J75" s="14">
         <v>46173</v>
@@ -7061,13 +7064,13 @@
         <v>237500</v>
       </c>
       <c r="Q75" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R75" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S75" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T75" s="19" t="s">
         <v>43</v>
@@ -7087,19 +7090,19 @@
         <v>22</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J76" s="14">
         <v>46173</v>
@@ -7123,13 +7126,13 @@
         <v>247500</v>
       </c>
       <c r="Q76" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R76" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S76" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T76" s="19" t="s">
         <v>43</v>
@@ -7149,19 +7152,19 @@
         <v>22</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J77" s="14">
         <v>46173</v>
@@ -7185,13 +7188,13 @@
         <v>245000</v>
       </c>
       <c r="Q77" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R77" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S77" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T77" s="19" t="s">
         <v>43</v>
@@ -7211,19 +7214,19 @@
         <v>22</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J78" s="14">
         <v>46173</v>
@@ -7273,19 +7276,19 @@
         <v>22</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J79" s="14">
         <v>46173</v>
@@ -7309,13 +7312,13 @@
         <v>230000</v>
       </c>
       <c r="Q79" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R79" s="19" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="S79" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T79" s="19" t="s">
         <v>43</v>
@@ -7335,19 +7338,19 @@
         <v>22</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J80" s="14">
         <v>46203</v>

--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -1346,9 +1346,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="25">
@@ -1392,31 +1392,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1437,24 +1413,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1469,9 +1438,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1480,13 +1472,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1499,7 +1484,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1520,14 +1512,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -1550,7 +1550,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1562,7 +1562,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1574,43 +1658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1622,49 +1670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1682,13 +1688,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1700,7 +1706,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1712,13 +1718,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1730,7 +1730,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1755,6 +1755,15 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1793,18 +1802,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1824,24 +1822,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1856,12 +1836,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1879,130 +1879,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3843,10 +3843,10 @@
         <v>40</v>
       </c>
       <c r="R23" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S23" s="19" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="T23" s="19" t="s">
         <v>43</v>
@@ -4460,13 +4460,13 @@
         <v>247500</v>
       </c>
       <c r="Q33" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R33" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S33" s="19" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="T33" s="19" t="s">
         <v>43</v>
@@ -4522,13 +4522,13 @@
         <v>245000</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R34" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S34" s="19" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="T34" s="19" t="s">
         <v>43</v>
@@ -5018,13 +5018,13 @@
         <v>375000</v>
       </c>
       <c r="Q42" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R42" s="19" t="s">
         <v>158</v>
       </c>
       <c r="S42" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T42" s="19" t="s">
         <v>43</v>
@@ -5210,7 +5210,7 @@
         <v>158</v>
       </c>
       <c r="S45" s="19" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="T45" s="19" t="s">
         <v>43</v>
@@ -5514,13 +5514,13 @@
         <v>245000</v>
       </c>
       <c r="Q50" s="19" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R50" s="19" t="s">
         <v>158</v>
       </c>
       <c r="S50" s="19" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="T50" s="19" t="s">
         <v>43</v>
@@ -6940,13 +6940,13 @@
         <v>475000</v>
       </c>
       <c r="Q73" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R73" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S73" s="19" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="T73" s="19" t="s">
         <v>43</v>

--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="441">
   <si>
     <t>Area</t>
   </si>
@@ -624,6 +624,9 @@
   </si>
   <si>
     <t>Mr. D.M.SAURI THARANGA DISSANAYAKA.</t>
+  </si>
+  <si>
+    <t>s=</t>
   </si>
   <si>
     <t>COLOMBO SOUTH</t>
@@ -1347,8 +1350,8 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="25">
@@ -1392,30 +1395,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1437,8 +1432,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1447,6 +1443,22 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1467,6 +1479,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -1484,7 +1504,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1497,14 +1517,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
@@ -1512,24 +1524,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1550,13 +1553,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1568,13 +1577,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1586,37 +1625,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1629,6 +1638,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1652,7 +1679,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1664,31 +1697,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1700,25 +1721,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1730,7 +1733,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1759,10 +1762,27 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1783,6 +1803,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1794,30 +1823,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1839,11 +1844,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1861,7 +1864,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1879,130 +1882,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3474,7 +3477,7 @@
         <v>41</v>
       </c>
       <c r="S17" s="18" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T17" s="19" t="s">
         <v>43</v>
@@ -3964,13 +3967,13 @@
         <v>495000</v>
       </c>
       <c r="Q25" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R25" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S25" s="19" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T25" s="19" t="s">
         <v>43</v>
@@ -4088,13 +4091,13 @@
         <v>495000</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R27" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S27" s="19" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T27" s="19" t="s">
         <v>43</v>
@@ -4218,39 +4221,39 @@
         <v>41</v>
       </c>
       <c r="S29" s="19" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T29" s="19" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J30" s="14">
         <v>46111</v>
@@ -4300,10 +4303,10 @@
         <v>186</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>25</v>
@@ -4312,7 +4315,7 @@
         <v>7701603390</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J31" s="14">
         <v>46111</v>
@@ -4336,13 +4339,13 @@
         <v>245000</v>
       </c>
       <c r="Q31" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R31" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S31" s="19" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T31" s="19" t="s">
         <v>43</v>
@@ -4362,19 +4365,19 @@
         <v>186</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J32" s="14">
         <v>46111</v>
@@ -4398,13 +4401,13 @@
         <v>247500</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R32" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S32" s="19" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T32" s="19" t="s">
         <v>43</v>
@@ -4424,19 +4427,19 @@
         <v>186</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J33" s="14">
         <v>46111</v>
@@ -4486,10 +4489,10 @@
         <v>186</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>25</v>
@@ -4498,7 +4501,7 @@
         <v>70602147</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J34" s="14">
         <v>46111</v>
@@ -4548,10 +4551,10 @@
         <v>192</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>25</v>
@@ -4560,7 +4563,7 @@
         <v>515701970</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J35" s="14">
         <v>46111</v>
@@ -4610,19 +4613,19 @@
         <v>192</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J36" s="14">
         <v>46111</v>
@@ -4660,31 +4663,31 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J37" s="14">
         <v>46112</v>
@@ -4714,7 +4717,7 @@
         <v>41</v>
       </c>
       <c r="S37" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T37" s="19" t="s">
         <v>43</v>
@@ -4722,31 +4725,31 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J38" s="14">
         <v>46112</v>
@@ -4790,25 +4793,25 @@
         <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J39" s="14">
         <v>46112</v>
@@ -4846,22 +4849,22 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>25</v>
@@ -4870,7 +4873,7 @@
         <v>679004406</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J40" s="14">
         <v>46112</v>
@@ -4920,19 +4923,19 @@
         <v>192</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J41" s="14">
         <v>46112</v>
@@ -4982,19 +4985,19 @@
         <v>192</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J42" s="14">
         <v>46112</v>
@@ -5044,10 +5047,10 @@
         <v>192</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>25</v>
@@ -5056,7 +5059,7 @@
         <v>6478802340</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J43" s="14">
         <v>46112</v>
@@ -5083,7 +5086,7 @@
         <v>28</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S43" s="19" t="s">
         <v>94</v>
@@ -5097,28 +5100,28 @@
         <v>183</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J44" s="14">
         <v>46112</v>
@@ -5162,16 +5165,16 @@
         <v>70</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>25</v>
@@ -5180,7 +5183,7 @@
         <v>106804280</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J45" s="14">
         <v>46112</v>
@@ -5218,22 +5221,22 @@
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>25</v>
@@ -5242,7 +5245,7 @@
         <v>5012804793</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J46" s="14">
         <v>46142</v>
@@ -5286,16 +5289,16 @@
         <v>33</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>25</v>
@@ -5304,7 +5307,7 @@
         <v>8986603515</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J47" s="14">
         <v>46112</v>
@@ -5354,19 +5357,19 @@
         <v>126</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J48" s="14">
         <v>46112</v>
@@ -5416,19 +5419,19 @@
         <v>174</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J49" s="14">
         <v>46142</v>
@@ -5478,19 +5481,19 @@
         <v>22</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J50" s="14">
         <v>46099</v>
@@ -5540,10 +5543,10 @@
         <v>22</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>25</v>
@@ -5552,7 +5555,7 @@
         <v>6801200161</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J51" s="14">
         <v>46100</v>
@@ -5596,16 +5599,16 @@
         <v>119</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>25</v>
@@ -5614,7 +5617,7 @@
         <v>7931304541</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J52" s="14">
         <v>46109</v>
@@ -5644,7 +5647,7 @@
         <v>41</v>
       </c>
       <c r="S52" s="19" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T52" s="19" t="s">
         <v>43</v>
@@ -5652,31 +5655,31 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J53" s="14">
         <v>46111</v>
@@ -5717,19 +5720,19 @@
         <v>183</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>25</v>
@@ -5738,7 +5741,7 @@
         <v>419502402</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J54" s="14">
         <v>46142</v>
@@ -5776,31 +5779,31 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J55" s="14">
         <v>46112</v>
@@ -5838,22 +5841,22 @@
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>25</v>
@@ -5862,7 +5865,7 @@
         <v>114404305</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J56" s="14">
         <v>46112</v>
@@ -5900,31 +5903,31 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J57" s="14">
         <v>46112</v>
@@ -5968,25 +5971,25 @@
         <v>33</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J58" s="14">
         <v>46142</v>
@@ -6030,25 +6033,25 @@
         <v>33</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J59" s="14">
         <v>46142</v>
@@ -6098,10 +6101,10 @@
         <v>121</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>25</v>
@@ -6110,7 +6113,7 @@
         <v>661101038</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J60" s="14">
         <v>46112</v>
@@ -6134,13 +6137,13 @@
         <v>495000</v>
       </c>
       <c r="Q60" s="19" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R60" s="19" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="S60" s="19" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="T60" s="19" t="s">
         <v>43</v>
@@ -6154,25 +6157,25 @@
         <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J61" s="14">
         <v>46112</v>
@@ -6216,25 +6219,25 @@
         <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J62" s="14">
         <v>46112</v>
@@ -6284,10 +6287,10 @@
         <v>22</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>25</v>
@@ -6296,7 +6299,7 @@
         <v>8915001242</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J63" s="14">
         <v>46112</v>
@@ -6346,10 +6349,10 @@
         <v>22</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>25</v>
@@ -6358,7 +6361,7 @@
         <v>162600148</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J64" s="14">
         <v>46112</v>
@@ -6402,16 +6405,16 @@
         <v>151</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>25</v>
@@ -6420,7 +6423,7 @@
         <v>162303825</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J65" s="14">
         <v>46173</v>
@@ -6470,19 +6473,19 @@
         <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J66" s="14">
         <v>46148</v>
@@ -6532,10 +6535,10 @@
         <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>25</v>
@@ -6544,7 +6547,7 @@
         <v>8005902216</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J67" s="14">
         <v>46150</v>
@@ -6594,10 +6597,10 @@
         <v>79</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>25</v>
@@ -6606,7 +6609,7 @@
         <v>7157401261</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J68" s="14">
         <v>46184</v>
@@ -6644,31 +6647,31 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J69" s="14">
         <v>46203</v>
@@ -6718,19 +6721,19 @@
         <v>22</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J70" s="14">
         <v>46196</v>
@@ -6780,19 +6783,19 @@
         <v>22</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J71" s="14">
         <v>46196</v>
@@ -6842,10 +6845,10 @@
         <v>22</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>25</v>
@@ -6854,7 +6857,7 @@
         <v>203402736</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J72" s="14">
         <v>46197</v>
@@ -6895,28 +6898,28 @@
         <v>150</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J73" s="14">
         <v>46203</v>
@@ -6966,19 +6969,19 @@
         <v>22</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J74" s="14">
         <v>46173</v>
@@ -7028,19 +7031,19 @@
         <v>22</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J75" s="14">
         <v>46173</v>
@@ -7090,19 +7093,19 @@
         <v>22</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J76" s="14">
         <v>46173</v>
@@ -7152,19 +7155,19 @@
         <v>22</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J77" s="14">
         <v>46173</v>
@@ -7214,19 +7217,19 @@
         <v>22</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J78" s="14">
         <v>46173</v>
@@ -7276,19 +7279,19 @@
         <v>22</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J79" s="14">
         <v>46173</v>
@@ -7338,19 +7341,19 @@
         <v>22</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J80" s="14">
         <v>46203</v>

--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="440">
   <si>
     <t>Area</t>
   </si>
@@ -146,9 +146,6 @@
   </si>
   <si>
     <t>CR SENT TO SFL</t>
-  </si>
-  <si>
-    <t>NOT SETTLED</t>
   </si>
   <si>
     <t>BOK-R25703</t>
@@ -305,6 +302,9 @@
     <t>SENT FOR CR CORRECTIONS</t>
   </si>
   <si>
+    <t>NOT SETTLED</t>
+  </si>
+  <si>
     <t>SOUTH AREA</t>
   </si>
   <si>
@@ -624,9 +624,6 @@
   </si>
   <si>
     <t>Mr. D.M.SAURI THARANGA DISSANAYAKA.</t>
-  </si>
-  <si>
-    <t>s=</t>
   </si>
   <si>
     <t>COLOMBO SOUTH</t>
@@ -1348,10 +1345,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="25">
@@ -1395,6 +1392,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -1402,7 +1406,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1410,9 +1414,32 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1424,9 +1451,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1441,15 +1467,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1458,30 +1476,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1495,44 +1528,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1553,19 +1550,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1577,7 +1562,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1589,43 +1580,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1637,7 +1598,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1655,13 +1616,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1679,13 +1676,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1697,31 +1688,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1733,7 +1718,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1762,17 +1759,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1803,11 +1818,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1827,21 +1848,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1850,27 +1856,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1882,130 +1879,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2427,6 +2424,7 @@
     <col min="18" max="18" width="34.1818181818182" customWidth="1"/>
     <col min="19" max="19" width="26.2727272727273" customWidth="1"/>
     <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="16384" width="8.72727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="52" spans="1:20">
@@ -2612,7 +2610,7 @@
         <v>42</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -2629,19 +2627,19 @@
         <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="J4" s="9">
         <v>46111</v>
@@ -2679,22 +2677,22 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>25</v>
@@ -2703,7 +2701,7 @@
         <v>251002814</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J5" s="9">
         <v>46112</v>
@@ -2747,25 +2745,25 @@
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="J6" s="9">
         <v>46112</v>
@@ -2792,7 +2790,7 @@
         <v>28</v>
       </c>
       <c r="R6" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S6" s="18" t="s">
         <v>30</v>
@@ -2803,22 +2801,22 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>25</v>
@@ -2827,7 +2825,7 @@
         <v>68310291</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J7" s="9">
         <v>46162</v>
@@ -2865,31 +2863,31 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="J8" s="9">
         <v>46192</v>
@@ -2927,31 +2925,31 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="J9" s="9">
         <v>46164</v>
@@ -2978,7 +2976,7 @@
         <v>28</v>
       </c>
       <c r="R9" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S9" s="18" t="s">
         <v>30</v>
@@ -3001,19 +2999,19 @@
         <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="J10" s="9">
         <v>46167</v>
@@ -3057,25 +3055,25 @@
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="J11" s="9">
         <v>46138</v>
@@ -3105,10 +3103,10 @@
         <v>41</v>
       </c>
       <c r="S11" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="T11" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -3232,7 +3230,7 @@
         <v>30</v>
       </c>
       <c r="T13" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -3294,7 +3292,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -3418,7 +3416,7 @@
         <v>30</v>
       </c>
       <c r="T16" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -3480,7 +3478,7 @@
         <v>42</v>
       </c>
       <c r="T17" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -3547,7 +3545,7 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>130</v>
@@ -3666,15 +3664,15 @@
         <v>42</v>
       </c>
       <c r="T20" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>144</v>
@@ -3801,10 +3799,10 @@
         <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>160</v>
@@ -3852,7 +3850,7 @@
         <v>42</v>
       </c>
       <c r="T23" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -3976,7 +3974,7 @@
         <v>42</v>
       </c>
       <c r="T25" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -4035,10 +4033,10 @@
         <v>41</v>
       </c>
       <c r="S26" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T26" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T26" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -4100,7 +4098,7 @@
         <v>42</v>
       </c>
       <c r="T27" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -4224,36 +4222,36 @@
         <v>42</v>
       </c>
       <c r="T29" s="19" t="s">
-        <v>202</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="J30" s="14">
         <v>46111</v>
@@ -4286,7 +4284,7 @@
         <v>158</v>
       </c>
       <c r="T30" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -4303,10 +4301,10 @@
         <v>186</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>25</v>
@@ -4315,7 +4313,7 @@
         <v>7701603390</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J31" s="14">
         <v>46111</v>
@@ -4348,7 +4346,7 @@
         <v>42</v>
       </c>
       <c r="T31" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -4365,19 +4363,19 @@
         <v>186</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="J32" s="14">
         <v>46111</v>
@@ -4410,7 +4408,7 @@
         <v>42</v>
       </c>
       <c r="T32" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -4427,19 +4425,19 @@
         <v>186</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="3" t="s">
+      <c r="I33" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="J33" s="14">
         <v>46111</v>
@@ -4472,7 +4470,7 @@
         <v>42</v>
       </c>
       <c r="T33" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -4489,10 +4487,10 @@
         <v>186</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>25</v>
@@ -4501,7 +4499,7 @@
         <v>70602147</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J34" s="14">
         <v>46111</v>
@@ -4534,7 +4532,7 @@
         <v>42</v>
       </c>
       <c r="T34" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -4551,10 +4549,10 @@
         <v>192</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>25</v>
@@ -4563,7 +4561,7 @@
         <v>515701970</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J35" s="14">
         <v>46111</v>
@@ -4613,19 +4611,19 @@
         <v>192</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="G36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="I36" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="J36" s="14">
         <v>46111</v>
@@ -4663,31 +4661,31 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H37" s="3" t="s">
+      <c r="I37" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="J37" s="14">
         <v>46112</v>
@@ -4717,39 +4715,39 @@
         <v>41</v>
       </c>
       <c r="S37" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T37" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="G38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H38" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="J38" s="14">
         <v>46112</v>
@@ -4779,10 +4777,10 @@
         <v>158</v>
       </c>
       <c r="S38" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T38" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T38" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -4793,25 +4791,25 @@
         <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="G39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H39" s="3" t="s">
+      <c r="I39" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="J39" s="14">
         <v>46112</v>
@@ -4844,27 +4842,27 @@
         <v>158</v>
       </c>
       <c r="T39" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="C40" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>25</v>
@@ -4873,7 +4871,7 @@
         <v>679004406</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J40" s="14">
         <v>46112</v>
@@ -4906,7 +4904,7 @@
         <v>158</v>
       </c>
       <c r="T40" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -4923,19 +4921,19 @@
         <v>192</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="G41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H41" s="3" t="s">
+      <c r="I41" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="J41" s="14">
         <v>46112</v>
@@ -4965,10 +4963,10 @@
         <v>158</v>
       </c>
       <c r="S41" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T41" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T41" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -4985,19 +4983,19 @@
         <v>192</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="J42" s="14">
         <v>46112</v>
@@ -5030,7 +5028,7 @@
         <v>30</v>
       </c>
       <c r="T42" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -5047,10 +5045,10 @@
         <v>192</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>25</v>
@@ -5059,7 +5057,7 @@
         <v>6478802340</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J43" s="14">
         <v>46112</v>
@@ -5086,13 +5084,13 @@
         <v>28</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S43" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T43" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T43" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -5100,28 +5098,28 @@
         <v>183</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>277</v>
       </c>
       <c r="J44" s="14">
         <v>46112</v>
@@ -5154,27 +5152,27 @@
         <v>158</v>
       </c>
       <c r="T44" s="19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="C45" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>25</v>
@@ -5183,7 +5181,7 @@
         <v>106804280</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J45" s="14">
         <v>46112</v>
@@ -5213,30 +5211,30 @@
         <v>158</v>
       </c>
       <c r="S45" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T45" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T45" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>25</v>
@@ -5245,7 +5243,7 @@
         <v>5012804793</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J46" s="14">
         <v>46142</v>
@@ -5278,7 +5276,7 @@
         <v>158</v>
       </c>
       <c r="T46" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -5289,16 +5287,16 @@
         <v>33</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>25</v>
@@ -5307,7 +5305,7 @@
         <v>8986603515</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J47" s="14">
         <v>46112</v>
@@ -5357,19 +5355,19 @@
         <v>126</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="G48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="J48" s="14">
         <v>46112</v>
@@ -5419,19 +5417,19 @@
         <v>174</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="G49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="J49" s="14">
         <v>46142</v>
@@ -5481,19 +5479,19 @@
         <v>22</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H50" s="3" t="s">
+      <c r="I50" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="J50" s="14">
         <v>46099</v>
@@ -5526,7 +5524,7 @@
         <v>30</v>
       </c>
       <c r="T50" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -5543,10 +5541,10 @@
         <v>22</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>25</v>
@@ -5555,7 +5553,7 @@
         <v>6801200161</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J51" s="14">
         <v>46100</v>
@@ -5599,16 +5597,16 @@
         <v>119</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="F52" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>25</v>
@@ -5617,7 +5615,7 @@
         <v>7931304541</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J52" s="14">
         <v>46109</v>
@@ -5650,36 +5648,36 @@
         <v>42</v>
       </c>
       <c r="T52" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="G53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H53" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="J53" s="14">
         <v>46111</v>
@@ -5709,10 +5707,10 @@
         <v>41</v>
       </c>
       <c r="S53" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T53" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T53" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -5720,19 +5718,19 @@
         <v>183</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>25</v>
@@ -5741,7 +5739,7 @@
         <v>419502402</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J54" s="14">
         <v>46142</v>
@@ -5774,36 +5772,36 @@
         <v>158</v>
       </c>
       <c r="T54" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H55" s="3" t="s">
+      <c r="I55" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>331</v>
       </c>
       <c r="J55" s="14">
         <v>46112</v>
@@ -5836,27 +5834,27 @@
         <v>158</v>
       </c>
       <c r="T55" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="E56" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>25</v>
@@ -5865,7 +5863,7 @@
         <v>114404305</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J56" s="14">
         <v>46112</v>
@@ -5898,36 +5896,36 @@
         <v>158</v>
       </c>
       <c r="T56" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="E57" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="G57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H57" s="3" t="s">
+      <c r="I57" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="J57" s="14">
         <v>46112</v>
@@ -5960,7 +5958,7 @@
         <v>158</v>
       </c>
       <c r="T57" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -5971,25 +5969,25 @@
         <v>33</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H58" s="3" t="s">
+      <c r="I58" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J58" s="14">
         <v>46142</v>
@@ -6022,7 +6020,7 @@
         <v>42</v>
       </c>
       <c r="T58" s="19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -6033,25 +6031,25 @@
         <v>33</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="G59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H59" s="3" t="s">
+      <c r="I59" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="J59" s="14">
         <v>46142</v>
@@ -6084,7 +6082,7 @@
         <v>158</v>
       </c>
       <c r="T59" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -6101,10 +6099,10 @@
         <v>121</v>
       </c>
       <c r="E60" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>25</v>
@@ -6113,7 +6111,7 @@
         <v>661101038</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J60" s="14">
         <v>46112</v>
@@ -6146,7 +6144,7 @@
         <v>42</v>
       </c>
       <c r="T60" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -6157,25 +6155,25 @@
         <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="F61" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H61" s="3" t="s">
+      <c r="I61" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="J61" s="14">
         <v>46112</v>
@@ -6219,25 +6217,25 @@
         <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="G62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H62" s="3" t="s">
+      <c r="I62" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="J62" s="14">
         <v>46112</v>
@@ -6267,10 +6265,10 @@
         <v>41</v>
       </c>
       <c r="S62" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T62" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T62" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -6287,10 +6285,10 @@
         <v>22</v>
       </c>
       <c r="E63" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>25</v>
@@ -6299,7 +6297,7 @@
         <v>8915001242</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J63" s="14">
         <v>46112</v>
@@ -6332,7 +6330,7 @@
         <v>158</v>
       </c>
       <c r="T63" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -6349,10 +6347,10 @@
         <v>22</v>
       </c>
       <c r="E64" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>25</v>
@@ -6361,7 +6359,7 @@
         <v>162600148</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J64" s="14">
         <v>46112</v>
@@ -6394,7 +6392,7 @@
         <v>42</v>
       </c>
       <c r="T64" s="19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -6405,16 +6403,16 @@
         <v>151</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>25</v>
@@ -6423,7 +6421,7 @@
         <v>162303825</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J65" s="14">
         <v>46173</v>
@@ -6453,39 +6451,39 @@
         <v>41</v>
       </c>
       <c r="S65" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T65" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="T65" s="19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:20">
       <c r="A66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E66" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H66" s="3" t="s">
+      <c r="I66" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="J66" s="14">
         <v>46148</v>
@@ -6529,16 +6527,16 @@
         <v>20</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E67" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>25</v>
@@ -6547,7 +6545,7 @@
         <v>8005902216</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J67" s="14">
         <v>46150</v>
@@ -6580,27 +6578,27 @@
         <v>30</v>
       </c>
       <c r="T67" s="19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E68" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>25</v>
@@ -6609,7 +6607,7 @@
         <v>7157401261</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J68" s="14">
         <v>46184</v>
@@ -6647,31 +6645,31 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="G69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H69" s="3" t="s">
+      <c r="I69" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="J69" s="14">
         <v>46203</v>
@@ -6721,19 +6719,19 @@
         <v>22</v>
       </c>
       <c r="E70" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="G70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H70" s="3" t="s">
+      <c r="I70" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="J70" s="14">
         <v>46196</v>
@@ -6766,7 +6764,7 @@
         <v>30</v>
       </c>
       <c r="T70" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -6783,19 +6781,19 @@
         <v>22</v>
       </c>
       <c r="E71" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="G71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H71" s="3" t="s">
+      <c r="I71" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="J71" s="14">
         <v>46196</v>
@@ -6828,7 +6826,7 @@
         <v>30</v>
       </c>
       <c r="T71" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -6845,10 +6843,10 @@
         <v>22</v>
       </c>
       <c r="E72" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>25</v>
@@ -6857,7 +6855,7 @@
         <v>203402736</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J72" s="14">
         <v>46197</v>
@@ -6890,7 +6888,7 @@
         <v>30</v>
       </c>
       <c r="T72" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -6898,28 +6896,28 @@
         <v>150</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="F73" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H73" s="3" t="s">
+      <c r="I73" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="J73" s="14">
         <v>46203</v>
@@ -6952,7 +6950,7 @@
         <v>42</v>
       </c>
       <c r="T73" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -6969,19 +6967,19 @@
         <v>22</v>
       </c>
       <c r="E74" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="G74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H74" s="3" t="s">
+      <c r="I74" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="J74" s="14">
         <v>46173</v>
@@ -7014,7 +7012,7 @@
         <v>30</v>
       </c>
       <c r="T74" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -7031,19 +7029,19 @@
         <v>22</v>
       </c>
       <c r="E75" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="G75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H75" s="3" t="s">
+      <c r="I75" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="J75" s="14">
         <v>46173</v>
@@ -7076,7 +7074,7 @@
         <v>30</v>
       </c>
       <c r="T75" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -7093,19 +7091,19 @@
         <v>22</v>
       </c>
       <c r="E76" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="G76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="J76" s="14">
         <v>46173</v>
@@ -7138,7 +7136,7 @@
         <v>30</v>
       </c>
       <c r="T76" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -7155,19 +7153,19 @@
         <v>22</v>
       </c>
       <c r="E77" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="G77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H77" s="3" t="s">
+      <c r="I77" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>428</v>
       </c>
       <c r="J77" s="14">
         <v>46173</v>
@@ -7200,7 +7198,7 @@
         <v>30</v>
       </c>
       <c r="T77" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -7217,19 +7215,19 @@
         <v>22</v>
       </c>
       <c r="E78" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="G78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="I78" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="J78" s="14">
         <v>46173</v>
@@ -7279,19 +7277,19 @@
         <v>22</v>
       </c>
       <c r="E79" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="G79" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H79" s="3" t="s">
+      <c r="I79" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="J79" s="14">
         <v>46173</v>
@@ -7324,7 +7322,7 @@
         <v>30</v>
       </c>
       <c r="T79" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -7341,19 +7339,19 @@
         <v>22</v>
       </c>
       <c r="E80" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="G80" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H80" s="3" t="s">
+      <c r="I80" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="J80" s="14">
         <v>46203</v>
@@ -7386,7 +7384,7 @@
         <v>30</v>
       </c>
       <c r="T80" s="19" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/UNPAID AND OVERDUE CREDIT SALES - BIKES/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{006D311D-324E-4AA5-B061-AA34F5950A01}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6910"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1343,15 +1349,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1392,150 +1395,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1548,194 +1414,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1758,311 +1438,69 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -2071,58 +1509,191 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2138,6 +1709,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2395,39 +1969,40 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1" filterMode="1"/>
   <dimension ref="A1:T80"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.0909090909091" customWidth="1"/>
-    <col min="2" max="2" width="26.0909090909091" customWidth="1"/>
-    <col min="3" max="3" width="11.3636363636364" customWidth="1"/>
-    <col min="4" max="4" width="15.9090909090909" customWidth="1"/>
-    <col min="5" max="5" width="12.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="15.08984375" customWidth="1"/>
+    <col min="2" max="2" width="26.08984375" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="8.27272727272727" customWidth="1"/>
-    <col min="8" max="8" width="11.8181818181818" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" customWidth="1"/>
     <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="9.45454545454546" customWidth="1"/>
-    <col min="11" max="11" width="6.54545454545455" customWidth="1"/>
-    <col min="12" max="12" width="9.36363636363636" customWidth="1"/>
-    <col min="13" max="13" width="8.63636363636364" customWidth="1"/>
-    <col min="14" max="14" width="8.18181818181818" customWidth="1"/>
-    <col min="15" max="15" width="13.4545454545455" customWidth="1"/>
-    <col min="16" max="16" width="13.7272727272727" customWidth="1"/>
-    <col min="17" max="17" width="40.1818181818182" customWidth="1"/>
-    <col min="18" max="18" width="34.1818181818182" customWidth="1"/>
-    <col min="19" max="19" width="26.2727272727273" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" customWidth="1"/>
+    <col min="11" max="11" width="6.54296875" customWidth="1"/>
+    <col min="12" max="12" width="9.36328125" customWidth="1"/>
+    <col min="13" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
+    <col min="16" max="16" width="13.7265625" customWidth="1"/>
+    <col min="17" max="17" width="40.1796875" customWidth="1"/>
+    <col min="18" max="18" width="34.1796875" customWidth="1"/>
+    <col min="19" max="19" width="26.26953125" customWidth="1"/>
     <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="16384" width="8.72727272727273" customWidth="1"/>
+    <col min="21" max="21" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" spans="1:20">
+    <row r="1" spans="1:20" ht="65">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2489,7 +2064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" hidden="1">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -2547,11 +2122,11 @@
       <c r="S2" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="19" t="s">
+      <c r="T2" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" hidden="1">
       <c r="A3" s="2" t="s">
         <v>32</v>
       </c>
@@ -2606,14 +2181,14 @@
       <c r="R3" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="19" t="s">
+      <c r="S3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="19" t="s">
+      <c r="T3" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" hidden="1">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2671,11 +2246,11 @@
       <c r="S4" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T4" s="19" t="s">
+      <c r="T4" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" hidden="1">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
@@ -2733,11 +2308,11 @@
       <c r="S5" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="19" t="s">
+      <c r="T5" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" hidden="1">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -2795,11 +2370,11 @@
       <c r="S6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="19" t="s">
+      <c r="T6" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" hidden="1">
       <c r="A7" s="2" t="s">
         <v>61</v>
       </c>
@@ -2854,14 +2429,14 @@
       <c r="R7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S7" s="19" t="s">
+      <c r="S7" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T7" s="19" t="s">
+      <c r="T7" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" hidden="1">
       <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
@@ -2916,14 +2491,14 @@
       <c r="R8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S8" s="19" t="s">
+      <c r="S8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T8" s="19" t="s">
+      <c r="T8" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" hidden="1">
       <c r="A9" s="2" t="s">
         <v>76</v>
       </c>
@@ -2981,11 +2556,11 @@
       <c r="S9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T9" s="19" t="s">
+      <c r="T9" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" hidden="1">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -3040,10 +2615,10 @@
       <c r="R10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S10" s="19" t="s">
+      <c r="S10" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T10" s="19" t="s">
+      <c r="T10" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3105,11 +2680,11 @@
       <c r="S11" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T11" s="19" t="s">
+      <c r="T11" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" hidden="1">
       <c r="A12" s="2" t="s">
         <v>95</v>
       </c>
@@ -3167,7 +2742,7 @@
       <c r="S12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T12" s="19" t="s">
+      <c r="T12" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3229,7 +2804,7 @@
       <c r="S13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T13" s="19" t="s">
+      <c r="T13" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3291,11 +2866,11 @@
       <c r="S14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T14" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="T14" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" hidden="1">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -3353,7 +2928,7 @@
       <c r="S15" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T15" s="19" t="s">
+      <c r="T15" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3415,8 +2990,8 @@
       <c r="S16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T16" s="19" t="s">
-        <v>94</v>
+      <c r="T16" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -3477,11 +3052,11 @@
       <c r="S17" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T17" s="19" t="s">
+      <c r="T17" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" hidden="1">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -3536,14 +3111,14 @@
       <c r="R18" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S18" s="19" t="s">
+      <c r="S18" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T18" s="19" t="s">
+      <c r="T18" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" hidden="1">
       <c r="A19" s="2" t="s">
         <v>61</v>
       </c>
@@ -3598,10 +3173,10 @@
       <c r="R19" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S19" s="19" t="s">
+      <c r="S19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T19" s="19" t="s">
+      <c r="T19" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3663,11 +3238,11 @@
       <c r="S20" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T20" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="T20" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" hidden="1">
       <c r="A21" s="3" t="s">
         <v>68</v>
       </c>
@@ -3716,20 +3291,20 @@
       <c r="P21" s="17">
         <v>475000</v>
       </c>
-      <c r="Q21" s="19" t="s">
+      <c r="Q21" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R21" s="19" t="s">
+      <c r="R21" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S21" s="19" t="s">
+      <c r="S21" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T21" s="19" t="s">
+      <c r="T21" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" hidden="1">
       <c r="A22" s="3" t="s">
         <v>150</v>
       </c>
@@ -3778,16 +3353,16 @@
       <c r="P22" s="17">
         <v>495000</v>
       </c>
-      <c r="Q22" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R22" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S22" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T22" s="19" t="s">
+      <c r="Q22" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R22" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S22" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T22" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3840,20 +3415,20 @@
       <c r="P23" s="17">
         <v>495000</v>
       </c>
-      <c r="Q23" s="19" t="s">
+      <c r="Q23" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R23" s="19" t="s">
+      <c r="R23" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S23" s="19" t="s">
+      <c r="S23" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T23" s="19" t="s">
+      <c r="T23" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" hidden="1">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
@@ -3902,16 +3477,16 @@
       <c r="P24" s="17">
         <v>495000</v>
       </c>
-      <c r="Q24" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R24" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S24" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T24" s="19" t="s">
+      <c r="Q24" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R24" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S24" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T24" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3964,17 +3539,17 @@
       <c r="P25" s="17">
         <v>495000</v>
       </c>
-      <c r="Q25" s="19" t="s">
+      <c r="Q25" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R25" s="19" t="s">
+      <c r="R25" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S25" s="19" t="s">
+      <c r="S25" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T25" s="19" t="s">
-        <v>94</v>
+      <c r="T25" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -4026,16 +3601,16 @@
       <c r="P26" s="17">
         <v>375000</v>
       </c>
-      <c r="Q26" s="19" t="s">
+      <c r="Q26" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R26" s="19" t="s">
+      <c r="R26" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S26" s="19" t="s">
+      <c r="S26" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T26" s="19" t="s">
+      <c r="T26" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4088,20 +3663,20 @@
       <c r="P27" s="17">
         <v>495000</v>
       </c>
-      <c r="Q27" s="19" t="s">
+      <c r="Q27" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R27" s="19" t="s">
+      <c r="R27" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S27" s="19" t="s">
+      <c r="S27" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T27" s="19" t="s">
+      <c r="T27" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" hidden="1">
       <c r="A28" s="3" t="s">
         <v>183</v>
       </c>
@@ -4150,16 +3725,16 @@
       <c r="P28" s="17">
         <v>247500</v>
       </c>
-      <c r="Q28" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R28" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S28" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T28" s="19" t="s">
+      <c r="Q28" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R28" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S28" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T28" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4212,17 +3787,17 @@
       <c r="P29" s="17">
         <v>495000</v>
       </c>
-      <c r="Q29" s="19" t="s">
+      <c r="Q29" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R29" s="19" t="s">
+      <c r="R29" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S29" s="19" t="s">
+      <c r="S29" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T29" s="19" t="s">
-        <v>94</v>
+      <c r="T29" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -4274,16 +3849,16 @@
       <c r="P30" s="17">
         <v>550000</v>
       </c>
-      <c r="Q30" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R30" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S30" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T30" s="19" t="s">
+      <c r="Q30" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R30" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S30" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T30" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4336,17 +3911,17 @@
       <c r="P31" s="17">
         <v>245000</v>
       </c>
-      <c r="Q31" s="19" t="s">
+      <c r="Q31" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R31" s="19" t="s">
+      <c r="R31" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S31" s="19" t="s">
+      <c r="S31" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T31" s="19" t="s">
-        <v>94</v>
+      <c r="T31" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -4398,17 +3973,17 @@
       <c r="P32" s="17">
         <v>247500</v>
       </c>
-      <c r="Q32" s="19" t="s">
+      <c r="Q32" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R32" s="19" t="s">
+      <c r="R32" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T32" s="19" t="s">
-        <v>94</v>
+      <c r="T32" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -4460,17 +4035,17 @@
       <c r="P33" s="17">
         <v>247500</v>
       </c>
-      <c r="Q33" s="19" t="s">
+      <c r="Q33" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R33" s="19" t="s">
+      <c r="R33" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S33" s="19" t="s">
+      <c r="S33" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T33" s="19" t="s">
-        <v>94</v>
+      <c r="T33" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -4522,20 +4097,20 @@
       <c r="P34" s="17">
         <v>245000</v>
       </c>
-      <c r="Q34" s="19" t="s">
+      <c r="Q34" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R34" s="19" t="s">
+      <c r="R34" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S34" s="19" t="s">
+      <c r="S34" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T34" s="19" t="s">
+      <c r="T34" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" hidden="1">
       <c r="A35" s="3" t="s">
         <v>183</v>
       </c>
@@ -4584,20 +4159,20 @@
       <c r="P35" s="17">
         <v>275000</v>
       </c>
-      <c r="Q35" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R35" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S35" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T35" s="19" t="s">
+      <c r="Q35" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R35" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S35" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T35" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" hidden="1">
       <c r="A36" s="3" t="s">
         <v>183</v>
       </c>
@@ -4646,16 +4221,16 @@
       <c r="P36" s="17">
         <v>275000</v>
       </c>
-      <c r="Q36" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R36" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S36" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T36" s="19" t="s">
+      <c r="Q36" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R36" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S36" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T36" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4708,17 +4283,17 @@
       <c r="P37" s="17">
         <v>550000</v>
       </c>
-      <c r="Q37" s="19" t="s">
+      <c r="Q37" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R37" s="19" t="s">
+      <c r="R37" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S37" s="19" t="s">
+      <c r="S37" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="T37" s="19" t="s">
-        <v>94</v>
+      <c r="T37" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -4770,16 +4345,16 @@
       <c r="P38" s="17">
         <v>475000</v>
       </c>
-      <c r="Q38" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R38" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S38" s="19" t="s">
+      <c r="Q38" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R38" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S38" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T38" s="19" t="s">
+      <c r="T38" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4832,16 +4407,16 @@
       <c r="P39" s="17">
         <v>375000</v>
       </c>
-      <c r="Q39" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R39" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S39" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T39" s="19" t="s">
+      <c r="Q39" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R39" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S39" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T39" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4894,16 +4469,16 @@
       <c r="P40" s="17">
         <v>475000</v>
       </c>
-      <c r="Q40" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R40" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S40" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T40" s="19" t="s">
+      <c r="Q40" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R40" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S40" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T40" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4956,16 +4531,16 @@
       <c r="P41" s="17">
         <v>325000</v>
       </c>
-      <c r="Q41" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R41" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S41" s="19" t="s">
+      <c r="Q41" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R41" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S41" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T41" s="19" t="s">
+      <c r="T41" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5018,16 +4593,16 @@
       <c r="P42" s="17">
         <v>375000</v>
       </c>
-      <c r="Q42" s="19" t="s">
+      <c r="Q42" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R42" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S42" s="19" t="s">
+      <c r="R42" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S42" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T42" s="19" t="s">
+      <c r="T42" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5080,20 +4655,20 @@
       <c r="P43" s="17">
         <v>385000</v>
       </c>
-      <c r="Q43" s="19" t="s">
+      <c r="Q43" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R43" s="20" t="s">
+      <c r="R43" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="S43" s="19" t="s">
+      <c r="S43" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T43" s="19" t="s">
+      <c r="T43" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" hidden="1">
       <c r="A44" s="3" t="s">
         <v>183</v>
       </c>
@@ -5142,16 +4717,16 @@
       <c r="P44" s="17">
         <v>475000</v>
       </c>
-      <c r="Q44" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R44" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S44" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T44" s="19" t="s">
+      <c r="Q44" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R44" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S44" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T44" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5204,17 +4779,17 @@
       <c r="P45" s="17">
         <v>550000</v>
       </c>
-      <c r="Q45" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R45" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S45" s="19" t="s">
+      <c r="Q45" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R45" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S45" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T45" s="19" t="s">
-        <v>94</v>
+      <c r="T45" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -5266,20 +4841,20 @@
       <c r="P46" s="17">
         <v>475000</v>
       </c>
-      <c r="Q46" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R46" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S46" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T46" s="19" t="s">
+      <c r="Q46" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R46" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S46" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T46" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" hidden="1">
       <c r="A47" s="3" t="s">
         <v>197</v>
       </c>
@@ -5328,20 +4903,20 @@
       <c r="P47" s="17">
         <v>550000</v>
       </c>
-      <c r="Q47" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R47" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S47" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T47" s="19" t="s">
+      <c r="Q47" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R47" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S47" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T47" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" hidden="1">
       <c r="A48" s="3" t="s">
         <v>197</v>
       </c>
@@ -5390,20 +4965,20 @@
       <c r="P48" s="17">
         <v>550000</v>
       </c>
-      <c r="Q48" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R48" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S48" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T48" s="19" t="s">
+      <c r="Q48" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R48" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S48" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T48" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:20" hidden="1">
       <c r="A49" s="3" t="s">
         <v>159</v>
       </c>
@@ -5452,16 +5027,16 @@
       <c r="P49" s="17">
         <v>550000</v>
       </c>
-      <c r="Q49" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R49" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S49" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T49" s="19" t="s">
+      <c r="Q49" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R49" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S49" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T49" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5514,20 +5089,20 @@
       <c r="P50" s="17">
         <v>245000</v>
       </c>
-      <c r="Q50" s="19" t="s">
+      <c r="Q50" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R50" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S50" s="19" t="s">
+      <c r="R50" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S50" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T50" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
+      <c r="T50" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" hidden="1">
       <c r="A51" s="3" t="s">
         <v>159</v>
       </c>
@@ -5576,16 +5151,16 @@
       <c r="P51" s="17">
         <v>300000</v>
       </c>
-      <c r="Q51" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R51" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S51" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T51" s="19" t="s">
+      <c r="Q51" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R51" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S51" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T51" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5638,17 +5213,17 @@
       <c r="P52" s="17">
         <v>495000</v>
       </c>
-      <c r="Q52" s="19" t="s">
+      <c r="Q52" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R52" s="19" t="s">
+      <c r="R52" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S52" s="19" t="s">
+      <c r="S52" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T52" s="19" t="s">
-        <v>94</v>
+      <c r="T52" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -5700,16 +5275,16 @@
       <c r="P53" s="17">
         <v>550000</v>
       </c>
-      <c r="Q53" s="19" t="s">
+      <c r="Q53" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R53" s="19" t="s">
+      <c r="R53" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S53" s="19" t="s">
+      <c r="S53" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T53" s="19" t="s">
+      <c r="T53" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5762,16 +5337,16 @@
       <c r="P54" s="17">
         <v>375000</v>
       </c>
-      <c r="Q54" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R54" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S54" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T54" s="19" t="s">
+      <c r="Q54" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R54" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S54" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T54" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5824,16 +5399,16 @@
       <c r="P55" s="17">
         <v>475000</v>
       </c>
-      <c r="Q55" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R55" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S55" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T55" s="19" t="s">
+      <c r="Q55" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R55" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S55" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T55" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5886,16 +5461,16 @@
       <c r="P56" s="17">
         <v>495000</v>
       </c>
-      <c r="Q56" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R56" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S56" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T56" s="19" t="s">
+      <c r="Q56" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R56" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S56" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T56" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5948,20 +5523,20 @@
       <c r="P57" s="17">
         <v>550000</v>
       </c>
-      <c r="Q57" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R57" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S57" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T57" s="19" t="s">
+      <c r="Q57" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R57" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S57" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T57" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:20" hidden="1">
       <c r="A58" s="3" t="s">
         <v>197</v>
       </c>
@@ -6010,16 +5585,16 @@
       <c r="P58" s="17">
         <v>375000</v>
       </c>
-      <c r="Q58" s="19" t="s">
+      <c r="Q58" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R58" s="19" t="s">
+      <c r="R58" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S58" s="19" t="s">
+      <c r="S58" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T58" s="19" t="s">
+      <c r="T58" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6072,16 +5647,16 @@
       <c r="P59" s="17">
         <v>475000</v>
       </c>
-      <c r="Q59" s="19" t="s">
+      <c r="Q59" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R59" s="19" t="s">
+      <c r="R59" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S59" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T59" s="19" t="s">
+      <c r="S59" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T59" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6134,20 +5709,20 @@
       <c r="P60" s="17">
         <v>495000</v>
       </c>
-      <c r="Q60" s="19" t="s">
+      <c r="Q60" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R60" s="19" t="s">
+      <c r="R60" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S60" s="19" t="s">
+      <c r="S60" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T60" s="19" t="s">
+      <c r="T60" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:20" hidden="1">
       <c r="A61" s="3" t="s">
         <v>159</v>
       </c>
@@ -6196,16 +5771,16 @@
       <c r="P61" s="17">
         <v>495000</v>
       </c>
-      <c r="Q61" s="19" t="s">
+      <c r="Q61" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R61" s="19" t="s">
+      <c r="R61" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S61" s="19" t="s">
+      <c r="S61" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T61" s="19" t="s">
+      <c r="T61" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6258,16 +5833,16 @@
       <c r="P62" s="17">
         <v>495000</v>
       </c>
-      <c r="Q62" s="19" t="s">
+      <c r="Q62" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R62" s="19" t="s">
+      <c r="R62" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S62" s="19" t="s">
+      <c r="S62" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T62" s="19" t="s">
+      <c r="T62" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6320,20 +5895,20 @@
       <c r="P63" s="17">
         <v>235000</v>
       </c>
-      <c r="Q63" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R63" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S63" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T63" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="Q63" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R63" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S63" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T63" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" hidden="1">
       <c r="A64" s="3" t="s">
         <v>159</v>
       </c>
@@ -6382,16 +5957,16 @@
       <c r="P64" s="17">
         <v>200000</v>
       </c>
-      <c r="Q64" s="19" t="s">
+      <c r="Q64" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R64" s="19" t="s">
+      <c r="R64" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S64" s="19" t="s">
+      <c r="S64" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T64" s="19" t="s">
+      <c r="T64" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6444,20 +6019,20 @@
       <c r="P65" s="17">
         <v>495000</v>
       </c>
-      <c r="Q65" s="19" t="s">
+      <c r="Q65" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R65" s="19" t="s">
+      <c r="R65" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S65" s="19" t="s">
+      <c r="S65" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="T65" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="T65" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" hidden="1">
       <c r="A66" s="3" t="s">
         <v>76</v>
       </c>
@@ -6506,20 +6081,20 @@
       <c r="P66" s="17">
         <v>550000</v>
       </c>
-      <c r="Q66" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R66" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S66" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T66" s="19" t="s">
+      <c r="Q66" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R66" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S66" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T66" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="1:20" hidden="1">
       <c r="A67" s="3" t="s">
         <v>159</v>
       </c>
@@ -6568,20 +6143,20 @@
       <c r="P67" s="17">
         <v>495000</v>
       </c>
-      <c r="Q67" s="19" t="s">
+      <c r="Q67" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R67" s="19" t="s">
+      <c r="R67" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S67" s="19" t="s">
+      <c r="S67" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T67" s="19" t="s">
+      <c r="T67" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="1:20" hidden="1">
       <c r="A68" s="3" t="s">
         <v>76</v>
       </c>
@@ -6630,20 +6205,20 @@
       <c r="P68" s="17">
         <v>475000</v>
       </c>
-      <c r="Q68" s="19" t="s">
+      <c r="Q68" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R68" s="19" t="s">
+      <c r="R68" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S68" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T68" s="19" t="s">
+      <c r="S68" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T68" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="1:20" hidden="1">
       <c r="A69" s="3" t="s">
         <v>386</v>
       </c>
@@ -6692,16 +6267,16 @@
       <c r="P69" s="17">
         <v>495000</v>
       </c>
-      <c r="Q69" s="19" t="s">
+      <c r="Q69" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R69" s="19" t="s">
+      <c r="R69" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S69" s="19" t="s">
+      <c r="S69" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T69" s="19" t="s">
+      <c r="T69" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6754,16 +6329,16 @@
       <c r="P70" s="17">
         <v>475000</v>
       </c>
-      <c r="Q70" s="19" t="s">
+      <c r="Q70" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R70" s="19" t="s">
+      <c r="R70" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S70" s="19" t="s">
+      <c r="S70" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T70" s="19" t="s">
+      <c r="T70" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6816,16 +6391,16 @@
       <c r="P71" s="17">
         <v>220000</v>
       </c>
-      <c r="Q71" s="19" t="s">
+      <c r="Q71" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R71" s="19" t="s">
+      <c r="R71" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S71" s="19" t="s">
+      <c r="S71" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T71" s="19" t="s">
+      <c r="T71" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6878,16 +6453,16 @@
       <c r="P72" s="17">
         <v>220000</v>
       </c>
-      <c r="Q72" s="19" t="s">
+      <c r="Q72" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R72" s="19" t="s">
+      <c r="R72" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S72" s="19" t="s">
+      <c r="S72" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T72" s="19" t="s">
+      <c r="T72" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6940,16 +6515,16 @@
       <c r="P73" s="17">
         <v>475000</v>
       </c>
-      <c r="Q73" s="19" t="s">
+      <c r="Q73" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R73" s="19" t="s">
+      <c r="R73" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S73" s="19" t="s">
+      <c r="S73" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="T73" s="19" t="s">
+      <c r="T73" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7002,16 +6577,16 @@
       <c r="P74" s="17">
         <v>125000</v>
       </c>
-      <c r="Q74" s="19" t="s">
+      <c r="Q74" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R74" s="19" t="s">
+      <c r="R74" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S74" s="19" t="s">
+      <c r="S74" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T74" s="19" t="s">
+      <c r="T74" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7064,17 +6639,17 @@
       <c r="P75" s="17">
         <v>237500</v>
       </c>
-      <c r="Q75" s="19" t="s">
+      <c r="Q75" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R75" s="19" t="s">
+      <c r="R75" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S75" s="19" t="s">
+      <c r="S75" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T75" s="19" t="s">
-        <v>94</v>
+      <c r="T75" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -7126,16 +6701,16 @@
       <c r="P76" s="17">
         <v>247500</v>
       </c>
-      <c r="Q76" s="19" t="s">
+      <c r="Q76" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R76" s="19" t="s">
+      <c r="R76" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S76" s="19" t="s">
+      <c r="S76" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T76" s="19" t="s">
+      <c r="T76" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7188,20 +6763,20 @@
       <c r="P77" s="17">
         <v>245000</v>
       </c>
-      <c r="Q77" s="19" t="s">
+      <c r="Q77" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R77" s="19" t="s">
+      <c r="R77" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S77" s="19" t="s">
+      <c r="S77" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T77" s="19" t="s">
+      <c r="T77" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:20">
+    <row r="78" spans="1:20" hidden="1">
       <c r="A78" s="3" t="s">
         <v>159</v>
       </c>
@@ -7250,16 +6825,16 @@
       <c r="P78" s="17">
         <v>205000</v>
       </c>
-      <c r="Q78" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="R78" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="S78" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="T78" s="19" t="s">
+      <c r="Q78" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R78" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S78" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T78" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7312,16 +6887,16 @@
       <c r="P79" s="17">
         <v>230000</v>
       </c>
-      <c r="Q79" s="19" t="s">
+      <c r="Q79" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R79" s="19" t="s">
+      <c r="R79" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="S79" s="19" t="s">
+      <c r="S79" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T79" s="19" t="s">
+      <c r="T79" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7374,74 +6949,80 @@
       <c r="P80" s="17">
         <v>190000</v>
       </c>
-      <c r="Q80" s="19" t="s">
+      <c r="Q80" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R80" s="19" t="s">
+      <c r="R80" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S80" s="19" t="s">
+      <c r="S80" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="T80" s="19" t="s">
+      <c r="T80" s="18" t="s">
         <v>94</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T80" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="19">
+      <filters>
+        <filter val="NOT SETTLED"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="E21:E60">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E66">
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E74">
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E75">
+    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E80">
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61:E62">
+    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E63:E64">
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E65:E66">
+    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E67:E68">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E69:E72">
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E73">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E74">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E75">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E76">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E78">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E60">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E75">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E74">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E66">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E80">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E61:E62">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E63:E64">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E65:E66">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E67:E68">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E69:E72">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E79:E80">
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/UNPAID AND OVERDUE CREDIT SALES - BIKES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="304" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E29B9F9C-F262-447C-93AB-E20C0A6F6DF4}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58AF52A0-FED0-4EF2-B702-B26A2F9BEC60}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$122</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1621,7 +1621,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1676,17 +1676,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2551,7 +2542,7 @@
       <c r="M2" s="10">
         <v>46309</v>
       </c>
-      <c r="N2" s="20">
+      <c r="N2" s="18">
         <f t="shared" ref="N2:N65" si="0">M2-L2</f>
         <v>119</v>
       </c>
@@ -2614,7 +2605,7 @@
       <c r="M3" s="10">
         <v>46309</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="18">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
@@ -2677,7 +2668,7 @@
       <c r="M4" s="10">
         <v>46309</v>
       </c>
-      <c r="N4" s="20">
+      <c r="N4" s="18">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
@@ -2740,7 +2731,7 @@
       <c r="M5" s="10">
         <v>46309</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -2803,7 +2794,7 @@
       <c r="M6" s="10">
         <v>46309</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -2866,7 +2857,7 @@
       <c r="M7" s="10">
         <v>46309</v>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="18">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
@@ -2929,7 +2920,7 @@
       <c r="M8" s="10">
         <v>46309</v>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="18">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
@@ -2992,7 +2983,7 @@
       <c r="M9" s="10">
         <v>46309</v>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="18">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
@@ -3055,7 +3046,7 @@
       <c r="M10" s="10">
         <v>46309</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="18">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
@@ -3118,7 +3109,7 @@
       <c r="M11" s="10">
         <v>46309</v>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="18">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
@@ -3181,7 +3172,7 @@
       <c r="M12" s="10">
         <v>46309</v>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="18">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
@@ -3244,7 +3235,7 @@
       <c r="M13" s="10">
         <v>46309</v>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="18">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
@@ -3307,7 +3298,7 @@
       <c r="M14" s="10">
         <v>46309</v>
       </c>
-      <c r="N14" s="20">
+      <c r="N14" s="18">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
@@ -3370,7 +3361,7 @@
       <c r="M15" s="10">
         <v>46309</v>
       </c>
-      <c r="N15" s="20">
+      <c r="N15" s="18">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
@@ -3433,7 +3424,7 @@
       <c r="M16" s="10">
         <v>46309</v>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="18">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
@@ -3496,7 +3487,7 @@
       <c r="M17" s="10">
         <v>46309</v>
       </c>
-      <c r="N17" s="20">
+      <c r="N17" s="18">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
@@ -3559,7 +3550,7 @@
       <c r="M18" s="10">
         <v>46309</v>
       </c>
-      <c r="N18" s="20">
+      <c r="N18" s="18">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
@@ -3622,7 +3613,7 @@
       <c r="M19" s="10">
         <v>46309</v>
       </c>
-      <c r="N19" s="20">
+      <c r="N19" s="18">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
@@ -3685,7 +3676,7 @@
       <c r="M20" s="10">
         <v>46309</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="18">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
@@ -3748,7 +3739,7 @@
       <c r="M21" s="10">
         <v>46309</v>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="18">
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
@@ -3811,7 +3802,7 @@
       <c r="M22" s="10">
         <v>46309</v>
       </c>
-      <c r="N22" s="20">
+      <c r="N22" s="18">
         <f t="shared" si="0"/>
         <v>167</v>
       </c>
@@ -3874,7 +3865,7 @@
       <c r="M23" s="10">
         <v>46309</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="18">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
@@ -3937,7 +3928,7 @@
       <c r="M24" s="10">
         <v>46309</v>
       </c>
-      <c r="N24" s="20">
+      <c r="N24" s="18">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
@@ -4000,7 +3991,7 @@
       <c r="M25" s="10">
         <v>46309</v>
       </c>
-      <c r="N25" s="20">
+      <c r="N25" s="18">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
@@ -4063,7 +4054,7 @@
       <c r="M26" s="10">
         <v>46309</v>
       </c>
-      <c r="N26" s="20">
+      <c r="N26" s="18">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
@@ -4126,7 +4117,7 @@
       <c r="M27" s="10">
         <v>46309</v>
       </c>
-      <c r="N27" s="20">
+      <c r="N27" s="18">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
@@ -4189,7 +4180,7 @@
       <c r="M28" s="10">
         <v>46309</v>
       </c>
-      <c r="N28" s="20">
+      <c r="N28" s="18">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
@@ -4252,7 +4243,7 @@
       <c r="M29" s="10">
         <v>46309</v>
       </c>
-      <c r="N29" s="20">
+      <c r="N29" s="18">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
@@ -4315,7 +4306,7 @@
       <c r="M30" s="10">
         <v>46309</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="18">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
@@ -4378,7 +4369,7 @@
       <c r="M31" s="10">
         <v>46309</v>
       </c>
-      <c r="N31" s="20">
+      <c r="N31" s="18">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
@@ -4441,7 +4432,7 @@
       <c r="M32" s="10">
         <v>46309</v>
       </c>
-      <c r="N32" s="20">
+      <c r="N32" s="18">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
@@ -4504,7 +4495,7 @@
       <c r="M33" s="10">
         <v>46309</v>
       </c>
-      <c r="N33" s="20">
+      <c r="N33" s="18">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
@@ -4567,7 +4558,7 @@
       <c r="M34" s="10">
         <v>46309</v>
       </c>
-      <c r="N34" s="20">
+      <c r="N34" s="18">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
@@ -4630,7 +4621,7 @@
       <c r="M35" s="10">
         <v>46309</v>
       </c>
-      <c r="N35" s="20">
+      <c r="N35" s="18">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
@@ -4693,7 +4684,7 @@
       <c r="M36" s="10">
         <v>46309</v>
       </c>
-      <c r="N36" s="20">
+      <c r="N36" s="18">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
@@ -4756,7 +4747,7 @@
       <c r="M37" s="10">
         <v>46309</v>
       </c>
-      <c r="N37" s="20">
+      <c r="N37" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -4819,7 +4810,7 @@
       <c r="M38" s="10">
         <v>46309</v>
       </c>
-      <c r="N38" s="20">
+      <c r="N38" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -4882,7 +4873,7 @@
       <c r="M39" s="10">
         <v>46309</v>
       </c>
-      <c r="N39" s="20">
+      <c r="N39" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -4945,7 +4936,7 @@
       <c r="M40" s="10">
         <v>46309</v>
       </c>
-      <c r="N40" s="20">
+      <c r="N40" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5008,7 +4999,7 @@
       <c r="M41" s="10">
         <v>46309</v>
       </c>
-      <c r="N41" s="20">
+      <c r="N41" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5071,7 +5062,7 @@
       <c r="M42" s="10">
         <v>46309</v>
       </c>
-      <c r="N42" s="20">
+      <c r="N42" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5134,7 +5125,7 @@
       <c r="M43" s="10">
         <v>46309</v>
       </c>
-      <c r="N43" s="20">
+      <c r="N43" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5197,7 +5188,7 @@
       <c r="M44" s="10">
         <v>46309</v>
       </c>
-      <c r="N44" s="20">
+      <c r="N44" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5260,7 +5251,7 @@
       <c r="M45" s="10">
         <v>46309</v>
       </c>
-      <c r="N45" s="20">
+      <c r="N45" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5323,7 +5314,7 @@
       <c r="M46" s="10">
         <v>46309</v>
       </c>
-      <c r="N46" s="20">
+      <c r="N46" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5386,7 +5377,7 @@
       <c r="M47" s="10">
         <v>46309</v>
       </c>
-      <c r="N47" s="20">
+      <c r="N47" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5449,7 +5440,7 @@
       <c r="M48" s="10">
         <v>46309</v>
       </c>
-      <c r="N48" s="20">
+      <c r="N48" s="18">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
@@ -5512,7 +5503,7 @@
       <c r="M49" s="10">
         <v>46309</v>
       </c>
-      <c r="N49" s="20">
+      <c r="N49" s="18">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
@@ -5575,7 +5566,7 @@
       <c r="M50" s="10">
         <v>46309</v>
       </c>
-      <c r="N50" s="20">
+      <c r="N50" s="18">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
@@ -5638,7 +5629,7 @@
       <c r="M51" s="10">
         <v>46309</v>
       </c>
-      <c r="N51" s="20">
+      <c r="N51" s="18">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
@@ -5701,7 +5692,7 @@
       <c r="M52" s="10">
         <v>46309</v>
       </c>
-      <c r="N52" s="20">
+      <c r="N52" s="18">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
@@ -5764,7 +5755,7 @@
       <c r="M53" s="10">
         <v>46309</v>
       </c>
-      <c r="N53" s="20">
+      <c r="N53" s="18">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
@@ -5827,7 +5818,7 @@
       <c r="M54" s="10">
         <v>46309</v>
       </c>
-      <c r="N54" s="20">
+      <c r="N54" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -5890,7 +5881,7 @@
       <c r="M55" s="10">
         <v>46309</v>
       </c>
-      <c r="N55" s="20">
+      <c r="N55" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -5953,7 +5944,7 @@
       <c r="M56" s="10">
         <v>46309</v>
       </c>
-      <c r="N56" s="20">
+      <c r="N56" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6016,7 +6007,7 @@
       <c r="M57" s="10">
         <v>46309</v>
       </c>
-      <c r="N57" s="20">
+      <c r="N57" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6079,7 +6070,7 @@
       <c r="M58" s="10">
         <v>46309</v>
       </c>
-      <c r="N58" s="20">
+      <c r="N58" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6142,7 +6133,7 @@
       <c r="M59" s="10">
         <v>46309</v>
       </c>
-      <c r="N59" s="20">
+      <c r="N59" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6205,7 +6196,7 @@
       <c r="M60" s="10">
         <v>46309</v>
       </c>
-      <c r="N60" s="20">
+      <c r="N60" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6268,7 +6259,7 @@
       <c r="M61" s="10">
         <v>46309</v>
       </c>
-      <c r="N61" s="20">
+      <c r="N61" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6331,7 +6322,7 @@
       <c r="M62" s="10">
         <v>46309</v>
       </c>
-      <c r="N62" s="20">
+      <c r="N62" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6394,7 +6385,7 @@
       <c r="M63" s="10">
         <v>46309</v>
       </c>
-      <c r="N63" s="20">
+      <c r="N63" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6457,7 +6448,7 @@
       <c r="M64" s="10">
         <v>46309</v>
       </c>
-      <c r="N64" s="20">
+      <c r="N64" s="18">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -6520,7 +6511,7 @@
       <c r="M65" s="10">
         <v>46309</v>
       </c>
-      <c r="N65" s="20">
+      <c r="N65" s="18">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
@@ -6583,7 +6574,7 @@
       <c r="M66" s="10">
         <v>46309</v>
       </c>
-      <c r="N66" s="20">
+      <c r="N66" s="18">
         <f t="shared" ref="N66:N80" si="1">M66-L66</f>
         <v>101</v>
       </c>
@@ -6646,7 +6637,7 @@
       <c r="M67" s="10">
         <v>46309</v>
       </c>
-      <c r="N67" s="20">
+      <c r="N67" s="18">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -6709,7 +6700,7 @@
       <c r="M68" s="10">
         <v>46309</v>
       </c>
-      <c r="N68" s="20">
+      <c r="N68" s="18">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
@@ -6772,7 +6763,7 @@
       <c r="M69" s="10">
         <v>46309</v>
       </c>
-      <c r="N69" s="20">
+      <c r="N69" s="18">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
@@ -6835,7 +6826,7 @@
       <c r="M70" s="10">
         <v>46309</v>
       </c>
-      <c r="N70" s="20">
+      <c r="N70" s="18">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
@@ -6898,7 +6889,7 @@
       <c r="M71" s="10">
         <v>46309</v>
       </c>
-      <c r="N71" s="20">
+      <c r="N71" s="18">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
@@ -6961,7 +6952,7 @@
       <c r="M72" s="10">
         <v>46309</v>
       </c>
-      <c r="N72" s="20">
+      <c r="N72" s="18">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
@@ -7024,7 +7015,7 @@
       <c r="M73" s="10">
         <v>46309</v>
       </c>
-      <c r="N73" s="20">
+      <c r="N73" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7087,7 +7078,7 @@
       <c r="M74" s="10">
         <v>46309</v>
       </c>
-      <c r="N74" s="20">
+      <c r="N74" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7150,7 +7141,7 @@
       <c r="M75" s="10">
         <v>46309</v>
       </c>
-      <c r="N75" s="20">
+      <c r="N75" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7213,7 +7204,7 @@
       <c r="M76" s="10">
         <v>46309</v>
       </c>
-      <c r="N76" s="20">
+      <c r="N76" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7276,7 +7267,7 @@
       <c r="M77" s="10">
         <v>46309</v>
       </c>
-      <c r="N77" s="20">
+      <c r="N77" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7339,7 +7330,7 @@
       <c r="M78" s="10">
         <v>46309</v>
       </c>
-      <c r="N78" s="20">
+      <c r="N78" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7402,7 +7393,7 @@
       <c r="M79" s="10">
         <v>46309</v>
       </c>
-      <c r="N79" s="20">
+      <c r="N79" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7465,7 +7456,7 @@
       <c r="M80" s="10">
         <v>46309</v>
       </c>
-      <c r="N80" s="20">
+      <c r="N80" s="18">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7489,48 +7480,48 @@
       </c>
     </row>
     <row r="81" spans="1:20">
-      <c r="A81" s="18" t="s">
+      <c r="A81" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="D81" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E81" s="18" t="s">
+      <c r="E81" s="3" t="s">
         <v>447</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="G81" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H81" s="18" t="s">
+      <c r="G81" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="I81" s="18" t="s">
+      <c r="I81" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="J81" s="19">
+      <c r="J81" s="13">
         <v>46234</v>
       </c>
-      <c r="K81" s="18">
+      <c r="K81" s="3">
         <v>60</v>
       </c>
-      <c r="L81" s="19">
-        <f>J81+K81</f>
+      <c r="L81" s="13">
+        <f t="shared" ref="L81:L122" si="2">J81+K81</f>
         <v>46294</v>
       </c>
       <c r="M81" s="10">
         <v>46309</v>
       </c>
-      <c r="N81" s="20">
-        <f>M81-L81</f>
+      <c r="N81" s="18">
+        <f t="shared" ref="N81:N122" si="3">M81-L81</f>
         <v>15</v>
       </c>
       <c r="O81" s="15">
@@ -7539,62 +7530,62 @@
       <c r="P81" s="15">
         <v>115000</v>
       </c>
-      <c r="Q81" s="22" t="s">
+      <c r="Q81" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R81" s="22" t="s">
+      <c r="R81" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S81" s="22" t="s">
+      <c r="S81" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T81" s="22" t="s">
+      <c r="T81" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:20">
-      <c r="A82" s="18" t="s">
+      <c r="A82" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B82" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="C82" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D82" s="18" t="s">
+      <c r="D82" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="E82" s="18" t="s">
+      <c r="E82" s="3" t="s">
         <v>465</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="G82" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H82" s="18">
+      <c r="G82" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" s="3">
         <v>6426802563</v>
       </c>
-      <c r="I82" s="18" t="s">
+      <c r="I82" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="J82" s="19">
+      <c r="J82" s="13">
         <v>46234</v>
       </c>
-      <c r="K82" s="18">
+      <c r="K82" s="3">
         <v>60</v>
       </c>
-      <c r="L82" s="19">
-        <f>J82+K82</f>
+      <c r="L82" s="13">
+        <f t="shared" si="2"/>
         <v>46294</v>
       </c>
       <c r="M82" s="10">
         <v>46309</v>
       </c>
-      <c r="N82" s="20">
-        <f>M82-L82</f>
+      <c r="N82" s="18">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="O82" s="15">
@@ -7603,62 +7594,62 @@
       <c r="P82" s="15">
         <v>315000</v>
       </c>
-      <c r="Q82" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R82" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S82" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T82" s="22" t="s">
+      <c r="Q82" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R82" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S82" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T82" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:20">
-      <c r="A83" s="18" t="s">
+      <c r="A83" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B83" s="18" t="s">
+      <c r="B83" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C83" s="18" t="s">
+      <c r="C83" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D83" s="18" t="s">
+      <c r="D83" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E83" s="3" t="s">
         <v>439</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="G83" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H83" s="18" t="s">
+      <c r="G83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="I83" s="18" t="s">
+      <c r="I83" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="J83" s="19">
+      <c r="J83" s="13">
         <v>46203</v>
       </c>
-      <c r="K83" s="18">
+      <c r="K83" s="3">
         <v>90</v>
       </c>
-      <c r="L83" s="19">
-        <f>J83+K83</f>
+      <c r="L83" s="13">
+        <f t="shared" si="2"/>
         <v>46293</v>
       </c>
       <c r="M83" s="10">
         <v>46309</v>
       </c>
-      <c r="N83" s="20">
-        <f>M83-L83</f>
+      <c r="N83" s="18">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="O83" s="15">
@@ -7667,62 +7658,62 @@
       <c r="P83" s="15">
         <v>150000</v>
       </c>
-      <c r="Q83" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R83" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S83" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T83" s="22" t="s">
+      <c r="Q83" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R83" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S83" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T83" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:20">
-      <c r="A84" s="18" t="s">
+      <c r="A84" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B84" s="18" t="s">
+      <c r="B84" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C84" s="18" t="s">
+      <c r="C84" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D84" s="18" t="s">
+      <c r="D84" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E84" s="18" t="s">
+      <c r="E84" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="G84" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H84" s="18">
+      <c r="G84" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" s="3">
         <v>9751002467</v>
       </c>
-      <c r="I84" s="18" t="s">
+      <c r="I84" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="J84" s="19">
+      <c r="J84" s="13">
         <v>46203</v>
       </c>
-      <c r="K84" s="18">
+      <c r="K84" s="3">
         <v>90</v>
       </c>
-      <c r="L84" s="19">
-        <f>J84+K84</f>
+      <c r="L84" s="13">
+        <f t="shared" si="2"/>
         <v>46293</v>
       </c>
       <c r="M84" s="10">
         <v>46309</v>
       </c>
-      <c r="N84" s="20">
-        <f>M84-L84</f>
+      <c r="N84" s="18">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="O84" s="15">
@@ -7731,62 +7722,62 @@
       <c r="P84" s="15">
         <v>220000</v>
       </c>
-      <c r="Q84" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R84" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S84" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T84" s="22" t="s">
+      <c r="Q84" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R84" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S84" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T84" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:20">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D85" s="18" t="s">
+      <c r="D85" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="3" t="s">
         <v>461</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="G85" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H85" s="18">
+      <c r="G85" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" s="3">
         <v>232302516</v>
       </c>
-      <c r="I85" s="18" t="s">
+      <c r="I85" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="J85" s="19">
+      <c r="J85" s="13">
         <v>46233</v>
       </c>
-      <c r="K85" s="18">
+      <c r="K85" s="3">
         <v>60</v>
       </c>
-      <c r="L85" s="19">
-        <f>J85+K85</f>
+      <c r="L85" s="13">
+        <f t="shared" si="2"/>
         <v>46293</v>
       </c>
       <c r="M85" s="10">
         <v>46309</v>
       </c>
-      <c r="N85" s="20">
-        <f>M85-L85</f>
+      <c r="N85" s="18">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="O85" s="15">
@@ -7795,62 +7786,62 @@
       <c r="P85" s="15">
         <v>315000</v>
       </c>
-      <c r="Q85" s="22" t="s">
+      <c r="Q85" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="R85" s="22" t="s">
+      <c r="R85" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="S85" s="22" t="s">
+      <c r="S85" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="T85" s="22" t="s">
+      <c r="T85" s="19" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="86" spans="1:20">
-      <c r="A86" s="18" t="s">
+      <c r="A86" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C86" s="18" t="s">
+      <c r="C86" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D86" s="18" t="s">
+      <c r="D86" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E86" s="18" t="s">
+      <c r="E86" s="3" t="s">
         <v>467</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="G86" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H86" s="18" t="s">
+      <c r="G86" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="I86" s="18" t="s">
+      <c r="I86" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="J86" s="19">
+      <c r="J86" s="13">
         <v>46232</v>
       </c>
-      <c r="K86" s="18">
+      <c r="K86" s="3">
         <v>60</v>
       </c>
-      <c r="L86" s="19">
-        <f>J86+K86</f>
+      <c r="L86" s="13">
+        <f t="shared" si="2"/>
         <v>46292</v>
       </c>
       <c r="M86" s="10">
         <v>46309</v>
       </c>
-      <c r="N86" s="20">
-        <f>M86-L86</f>
+      <c r="N86" s="18">
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="O86" s="15">
@@ -7859,62 +7850,62 @@
       <c r="P86" s="15">
         <v>297000</v>
       </c>
-      <c r="Q86" s="22" t="s">
+      <c r="Q86" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="R86" s="22" t="s">
+      <c r="R86" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="S86" s="22" t="s">
+      <c r="S86" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T86" s="22" t="s">
+      <c r="T86" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:20">
-      <c r="A87" s="18" t="s">
+      <c r="A87" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C87" s="18" t="s">
+      <c r="C87" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D87" s="18" t="s">
+      <c r="D87" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E87" s="18" t="s">
+      <c r="E87" s="3" t="s">
         <v>470</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="G87" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H87" s="18" t="s">
+      <c r="G87" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="I87" s="18" t="s">
+      <c r="I87" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="J87" s="19">
+      <c r="J87" s="13">
         <v>46232</v>
       </c>
-      <c r="K87" s="18">
+      <c r="K87" s="3">
         <v>60</v>
       </c>
-      <c r="L87" s="19">
-        <f>J87+K87</f>
+      <c r="L87" s="13">
+        <f t="shared" si="2"/>
         <v>46292</v>
       </c>
       <c r="M87" s="10">
         <v>46309</v>
       </c>
-      <c r="N87" s="20">
-        <f>M87-L87</f>
+      <c r="N87" s="18">
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="O87" s="15">
@@ -7923,62 +7914,62 @@
       <c r="P87" s="15">
         <v>220000</v>
       </c>
-      <c r="Q87" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R87" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S87" s="22" t="s">
+      <c r="Q87" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R87" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S87" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T87" s="22" t="s">
+      <c r="T87" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:20">
-      <c r="A88" s="18" t="s">
+      <c r="A88" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B88" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C88" s="18" t="s">
+      <c r="C88" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D88" s="18" t="s">
+      <c r="D88" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E88" s="18" t="s">
+      <c r="E88" s="3" t="s">
         <v>452</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="G88" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H88" s="18">
+      <c r="G88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" s="3">
         <v>9535104354</v>
       </c>
-      <c r="I88" s="18" t="s">
+      <c r="I88" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="J88" s="19">
+      <c r="J88" s="13">
         <v>46231</v>
       </c>
-      <c r="K88" s="18">
+      <c r="K88" s="3">
         <v>60</v>
       </c>
-      <c r="L88" s="19">
-        <f>J88+K88</f>
+      <c r="L88" s="13">
+        <f t="shared" si="2"/>
         <v>46291</v>
       </c>
       <c r="M88" s="10">
         <v>46309</v>
       </c>
-      <c r="N88" s="20">
-        <f>M88-L88</f>
+      <c r="N88" s="18">
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="O88" s="15">
@@ -7987,62 +7978,62 @@
       <c r="P88" s="15">
         <v>315000</v>
       </c>
-      <c r="Q88" s="22" t="s">
+      <c r="Q88" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R88" s="22" t="s">
+      <c r="R88" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S88" s="22" t="s">
+      <c r="S88" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T88" s="22" t="s">
+      <c r="T88" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:20">
-      <c r="A89" s="18" t="s">
+      <c r="A89" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C89" s="18" t="s">
+      <c r="C89" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D89" s="18" t="s">
+      <c r="D89" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E89" s="18" t="s">
+      <c r="E89" s="3" t="s">
         <v>455</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="G89" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H89" s="18" t="s">
+      <c r="G89" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="I89" s="18" t="s">
+      <c r="I89" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="J89" s="19">
+      <c r="J89" s="13">
         <v>46227</v>
       </c>
-      <c r="K89" s="18">
+      <c r="K89" s="3">
         <v>60</v>
       </c>
-      <c r="L89" s="19">
-        <f>J89+K89</f>
+      <c r="L89" s="13">
+        <f t="shared" si="2"/>
         <v>46287</v>
       </c>
       <c r="M89" s="10">
         <v>46309</v>
       </c>
-      <c r="N89" s="20">
-        <f>M89-L89</f>
+      <c r="N89" s="18">
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="O89" s="15">
@@ -8051,62 +8042,62 @@
       <c r="P89" s="15">
         <v>550000</v>
       </c>
-      <c r="Q89" s="22" t="s">
+      <c r="Q89" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R89" s="22" t="s">
+      <c r="R89" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S89" s="22" t="s">
+      <c r="S89" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T89" s="22" t="s">
+      <c r="T89" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:20">
-      <c r="A90" s="18" t="s">
+      <c r="A90" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C90" s="18" t="s">
+      <c r="C90" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D90" s="18" t="s">
+      <c r="D90" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E90" s="18" t="s">
+      <c r="E90" s="3" t="s">
         <v>458</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="G90" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H90" s="18" t="s">
+      <c r="G90" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="I90" s="18" t="s">
+      <c r="I90" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="J90" s="19">
+      <c r="J90" s="13">
         <v>46225</v>
       </c>
-      <c r="K90" s="18">
+      <c r="K90" s="3">
         <v>60</v>
       </c>
-      <c r="L90" s="19">
-        <f>J90+K90</f>
+      <c r="L90" s="13">
+        <f t="shared" si="2"/>
         <v>46285</v>
       </c>
       <c r="M90" s="10">
         <v>46309</v>
       </c>
-      <c r="N90" s="20">
-        <f>M90-L90</f>
+      <c r="N90" s="18">
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="O90" s="15">
@@ -8115,62 +8106,62 @@
       <c r="P90" s="15">
         <v>220000</v>
       </c>
-      <c r="Q90" s="22" t="s">
+      <c r="Q90" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="R90" s="22" t="s">
+      <c r="R90" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="S90" s="22" t="s">
+      <c r="S90" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T90" s="22" t="s">
+      <c r="T90" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:20">
-      <c r="A91" s="18" t="s">
+      <c r="A91" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B91" s="18" t="s">
+      <c r="B91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C91" s="18" t="s">
+      <c r="C91" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D91" s="18" t="s">
+      <c r="D91" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E91" s="18" t="s">
+      <c r="E91" s="3" t="s">
         <v>473</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="G91" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H91" s="18" t="s">
+      <c r="G91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I91" s="18" t="s">
+      <c r="I91" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="J91" s="19">
+      <c r="J91" s="13">
         <v>46190</v>
       </c>
-      <c r="K91" s="18">
+      <c r="K91" s="3">
         <v>90</v>
       </c>
-      <c r="L91" s="19">
-        <f>J91+K91</f>
+      <c r="L91" s="13">
+        <f t="shared" si="2"/>
         <v>46280</v>
       </c>
       <c r="M91" s="10">
         <v>46309</v>
       </c>
-      <c r="N91" s="20">
-        <f>M91-L91</f>
+      <c r="N91" s="18">
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="O91" s="15">
@@ -8179,62 +8170,62 @@
       <c r="P91" s="15">
         <v>550000</v>
       </c>
-      <c r="Q91" s="22" t="s">
+      <c r="Q91" s="19" t="s">
         <v>27</v>
       </c>
       <c r="R91" s="16" t="s">
         <v>489</v>
       </c>
-      <c r="S91" s="22" t="s">
+      <c r="S91" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T91" s="22" t="s">
+      <c r="T91" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:20">
-      <c r="A92" s="18" t="s">
+      <c r="A92" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B92" s="18" t="s">
+      <c r="B92" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C92" s="18" t="s">
+      <c r="C92" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="D92" s="18" t="s">
+      <c r="D92" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="E92" s="18" t="s">
+      <c r="E92" s="3" t="s">
         <v>406</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="G92" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H92" s="18" t="s">
+      <c r="G92" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="I92" s="18" t="s">
+      <c r="I92" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="J92" s="19">
+      <c r="J92" s="13">
         <v>46203</v>
       </c>
-      <c r="K92" s="18">
+      <c r="K92" s="3">
         <v>60</v>
       </c>
-      <c r="L92" s="19">
-        <f>J92+K92</f>
+      <c r="L92" s="13">
+        <f t="shared" si="2"/>
         <v>46263</v>
       </c>
       <c r="M92" s="10">
         <v>46309</v>
       </c>
-      <c r="N92" s="20">
-        <f>M92-L92</f>
+      <c r="N92" s="18">
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="O92" s="15">
@@ -8243,62 +8234,62 @@
       <c r="P92" s="15">
         <v>475000</v>
       </c>
-      <c r="Q92" s="22" t="s">
+      <c r="Q92" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R92" s="22" t="s">
+      <c r="R92" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S92" s="22" t="s">
+      <c r="S92" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T92" s="22" t="s">
+      <c r="T92" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:20">
-      <c r="A93" s="18" t="s">
+      <c r="A93" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B93" s="18" t="s">
+      <c r="B93" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="18" t="s">
+      <c r="C93" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E93" s="18" t="s">
+      <c r="E93" s="3" t="s">
         <v>410</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="G93" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H93" s="18" t="s">
+      <c r="G93" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="I93" s="18" t="s">
+      <c r="I93" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="J93" s="19">
+      <c r="J93" s="13">
         <v>46173</v>
       </c>
-      <c r="K93" s="18">
+      <c r="K93" s="3">
         <v>90</v>
       </c>
-      <c r="L93" s="19">
-        <f>J93+K93</f>
+      <c r="L93" s="13">
+        <f t="shared" si="2"/>
         <v>46263</v>
       </c>
       <c r="M93" s="10">
         <v>46309</v>
       </c>
-      <c r="N93" s="20">
-        <f>M93-L93</f>
+      <c r="N93" s="18">
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="O93" s="15">
@@ -8307,62 +8298,62 @@
       <c r="P93" s="15">
         <v>125000</v>
       </c>
-      <c r="Q93" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R93" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S93" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T93" s="22" t="s">
+      <c r="Q93" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R93" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S93" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T93" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:20">
-      <c r="A94" s="18" t="s">
+      <c r="A94" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B94" s="18" t="s">
+      <c r="B94" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C94" s="18" t="s">
+      <c r="C94" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D94" s="18" t="s">
+      <c r="D94" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E94" s="18" t="s">
+      <c r="E94" s="3" t="s">
         <v>418</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="G94" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H94" s="18" t="s">
+      <c r="G94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="I94" s="18" t="s">
+      <c r="I94" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="J94" s="19">
+      <c r="J94" s="13">
         <v>46173</v>
       </c>
-      <c r="K94" s="18">
+      <c r="K94" s="3">
         <v>90</v>
       </c>
-      <c r="L94" s="19">
-        <f>J94+K94</f>
+      <c r="L94" s="13">
+        <f t="shared" si="2"/>
         <v>46263</v>
       </c>
       <c r="M94" s="10">
         <v>46309</v>
       </c>
-      <c r="N94" s="20">
-        <f>M94-L94</f>
+      <c r="N94" s="18">
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="O94" s="15">
@@ -8371,62 +8362,62 @@
       <c r="P94" s="15">
         <v>247500</v>
       </c>
-      <c r="Q94" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R94" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S94" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T94" s="22" t="s">
+      <c r="Q94" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R94" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S94" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T94" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:20">
-      <c r="A95" s="18" t="s">
+      <c r="A95" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B95" s="18" t="s">
+      <c r="B95" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C95" s="18" t="s">
+      <c r="C95" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D95" s="18" t="s">
+      <c r="D95" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E95" s="18" t="s">
+      <c r="E95" s="3" t="s">
         <v>422</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="G95" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H95" s="18" t="s">
+      <c r="G95" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="I95" s="18" t="s">
+      <c r="I95" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="J95" s="19">
+      <c r="J95" s="13">
         <v>46173</v>
       </c>
-      <c r="K95" s="18">
+      <c r="K95" s="3">
         <v>90</v>
       </c>
-      <c r="L95" s="19">
-        <f>J95+K95</f>
+      <c r="L95" s="13">
+        <f t="shared" si="2"/>
         <v>46263</v>
       </c>
       <c r="M95" s="10">
         <v>46309</v>
       </c>
-      <c r="N95" s="20">
-        <f>M95-L95</f>
+      <c r="N95" s="18">
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="O95" s="15">
@@ -8435,62 +8426,62 @@
       <c r="P95" s="15">
         <v>245000</v>
       </c>
-      <c r="Q95" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R95" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S95" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T95" s="22" t="s">
+      <c r="Q95" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R95" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S95" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T95" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:20">
-      <c r="A96" s="18" t="s">
+      <c r="A96" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B96" s="18" t="s">
+      <c r="B96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C96" s="18" t="s">
+      <c r="C96" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D96" s="18" t="s">
+      <c r="D96" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E96" s="18" t="s">
+      <c r="E96" s="3" t="s">
         <v>430</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="G96" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H96" s="18" t="s">
+      <c r="G96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="I96" s="18" t="s">
+      <c r="I96" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="J96" s="19">
+      <c r="J96" s="13">
         <v>46173</v>
       </c>
-      <c r="K96" s="18">
+      <c r="K96" s="3">
         <v>90</v>
       </c>
-      <c r="L96" s="19">
-        <f>J96+K96</f>
+      <c r="L96" s="13">
+        <f t="shared" si="2"/>
         <v>46263</v>
       </c>
       <c r="M96" s="10">
         <v>46309</v>
       </c>
-      <c r="N96" s="20">
-        <f>M96-L96</f>
+      <c r="N96" s="18">
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="O96" s="15">
@@ -8499,62 +8490,62 @@
       <c r="P96" s="15">
         <v>230000</v>
       </c>
-      <c r="Q96" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R96" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S96" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T96" s="22" t="s">
+      <c r="Q96" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R96" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S96" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T96" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:20">
-      <c r="A97" s="18" t="s">
+      <c r="A97" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="B97" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="18" t="s">
+      <c r="C97" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D97" s="18" t="s">
+      <c r="D97" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E97" s="18" t="s">
+      <c r="E97" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="G97" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H97" s="18" t="s">
+      <c r="G97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="I97" s="18" t="s">
+      <c r="I97" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="J97" s="19">
+      <c r="J97" s="13">
         <v>46203</v>
       </c>
-      <c r="K97" s="18">
+      <c r="K97" s="3">
         <v>60</v>
       </c>
-      <c r="L97" s="19">
-        <f>J97+K97</f>
+      <c r="L97" s="13">
+        <f t="shared" si="2"/>
         <v>46263</v>
       </c>
       <c r="M97" s="10">
         <v>46309</v>
       </c>
-      <c r="N97" s="20">
-        <f>M97-L97</f>
+      <c r="N97" s="18">
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="O97" s="15">
@@ -8563,62 +8554,62 @@
       <c r="P97" s="15">
         <v>190000</v>
       </c>
-      <c r="Q97" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R97" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S97" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T97" s="22" t="s">
+      <c r="Q97" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R97" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S97" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T97" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:20">
-      <c r="A98" s="18" t="s">
+      <c r="A98" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B98" s="18" t="s">
+      <c r="B98" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C98" s="18" t="s">
+      <c r="C98" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D98" s="18" t="s">
+      <c r="D98" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E98" s="18" t="s">
+      <c r="E98" s="3" t="s">
         <v>400</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="G98" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H98" s="18">
+      <c r="G98" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="3">
         <v>203402736</v>
       </c>
-      <c r="I98" s="18" t="s">
+      <c r="I98" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="J98" s="19">
+      <c r="J98" s="13">
         <v>46197</v>
       </c>
-      <c r="K98" s="18">
+      <c r="K98" s="3">
         <v>60</v>
       </c>
-      <c r="L98" s="19">
-        <f>J98+K98</f>
+      <c r="L98" s="13">
+        <f t="shared" si="2"/>
         <v>46257</v>
       </c>
       <c r="M98" s="10">
         <v>46309</v>
       </c>
-      <c r="N98" s="20">
-        <f>M98-L98</f>
+      <c r="N98" s="18">
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="O98" s="15">
@@ -8627,62 +8618,62 @@
       <c r="P98" s="15">
         <v>220000</v>
       </c>
-      <c r="Q98" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R98" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S98" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T98" s="22" t="s">
+      <c r="Q98" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R98" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S98" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T98" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:20">
-      <c r="A99" s="18" t="s">
+      <c r="A99" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C99" s="18" t="s">
+      <c r="C99" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D99" s="18" t="s">
+      <c r="D99" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E99" s="18" t="s">
+      <c r="E99" s="3" t="s">
         <v>392</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="G99" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H99" s="18" t="s">
+      <c r="G99" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="I99" s="18" t="s">
+      <c r="I99" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="J99" s="19">
+      <c r="J99" s="13">
         <v>46196</v>
       </c>
-      <c r="K99" s="18">
+      <c r="K99" s="3">
         <v>60</v>
       </c>
-      <c r="L99" s="19">
-        <f>J99+K99</f>
+      <c r="L99" s="13">
+        <f t="shared" si="2"/>
         <v>46256</v>
       </c>
       <c r="M99" s="10">
         <v>46309</v>
       </c>
-      <c r="N99" s="20">
-        <f>M99-L99</f>
+      <c r="N99" s="18">
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="O99" s="15">
@@ -8691,62 +8682,62 @@
       <c r="P99" s="15">
         <v>190000</v>
       </c>
-      <c r="Q99" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R99" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S99" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T99" s="22" t="s">
+      <c r="Q99" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R99" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S99" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T99" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:20">
-      <c r="A100" s="18" t="s">
+      <c r="A100" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C100" s="18" t="s">
+      <c r="C100" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D100" s="18" t="s">
+      <c r="D100" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E100" s="18" t="s">
+      <c r="E100" s="3" t="s">
         <v>396</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="G100" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H100" s="18" t="s">
+      <c r="G100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="I100" s="18" t="s">
+      <c r="I100" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="J100" s="19">
+      <c r="J100" s="13">
         <v>46196</v>
       </c>
-      <c r="K100" s="18">
+      <c r="K100" s="3">
         <v>60</v>
       </c>
-      <c r="L100" s="19">
-        <f>J100+K100</f>
+      <c r="L100" s="13">
+        <f t="shared" si="2"/>
         <v>46256</v>
       </c>
       <c r="M100" s="10">
         <v>46309</v>
       </c>
-      <c r="N100" s="20">
-        <f>M100-L100</f>
+      <c r="N100" s="18">
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="O100" s="15">
@@ -8755,62 +8746,62 @@
       <c r="P100" s="15">
         <v>220000</v>
       </c>
-      <c r="Q100" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R100" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S100" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T100" s="22" t="s">
+      <c r="Q100" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R100" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S100" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T100" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="101" spans="1:20">
-      <c r="A101" s="18" t="s">
+      <c r="A101" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C101" s="18" t="s">
+      <c r="C101" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D101" s="18" t="s">
+      <c r="D101" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E101" s="18" t="s">
+      <c r="E101" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G101" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H101" s="18">
+      <c r="G101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="3">
         <v>7881200699</v>
       </c>
-      <c r="I101" s="18" t="s">
+      <c r="I101" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J101" s="19">
+      <c r="J101" s="13">
         <v>46142</v>
       </c>
-      <c r="K101" s="18">
+      <c r="K101" s="3">
         <v>90</v>
       </c>
-      <c r="L101" s="19">
-        <f>J101+K101</f>
+      <c r="L101" s="13">
+        <f t="shared" si="2"/>
         <v>46232</v>
       </c>
       <c r="M101" s="10">
         <v>46309</v>
       </c>
-      <c r="N101" s="20">
-        <f>M101-L101</f>
+      <c r="N101" s="18">
+        <f t="shared" si="3"/>
         <v>77</v>
       </c>
       <c r="O101" s="15">
@@ -8819,62 +8810,62 @@
       <c r="P101" s="15">
         <v>495000</v>
       </c>
-      <c r="Q101" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R101" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S101" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T101" s="22" t="s">
+      <c r="Q101" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R101" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S101" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T101" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:20">
-      <c r="A102" s="18" t="s">
+      <c r="A102" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C102" s="18" t="s">
+      <c r="C102" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D102" s="18" t="s">
+      <c r="D102" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E102" s="18" t="s">
+      <c r="E102" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G102" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H102" s="18" t="s">
+      <c r="G102" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I102" s="18" t="s">
+      <c r="I102" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="J102" s="19">
+      <c r="J102" s="13">
         <v>46138</v>
       </c>
-      <c r="K102" s="18">
+      <c r="K102" s="3">
         <v>90</v>
       </c>
-      <c r="L102" s="19">
-        <f>J102+K102</f>
+      <c r="L102" s="13">
+        <f t="shared" si="2"/>
         <v>46228</v>
       </c>
       <c r="M102" s="10">
         <v>46309</v>
       </c>
-      <c r="N102" s="20">
-        <f>M102-L102</f>
+      <c r="N102" s="18">
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="O102" s="15">
@@ -8883,62 +8874,62 @@
       <c r="P102" s="15">
         <v>495000</v>
       </c>
-      <c r="Q102" s="22" t="s">
+      <c r="Q102" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R102" s="22" t="s">
+      <c r="R102" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S102" s="22" t="s">
+      <c r="S102" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T102" s="22" t="s">
+      <c r="T102" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="103" spans="1:20">
-      <c r="A103" s="18" t="s">
+      <c r="A103" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C103" s="18" t="s">
+      <c r="C103" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D103" s="18" t="s">
+      <c r="D103" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E103" s="18" t="s">
+      <c r="E103" s="3" t="s">
         <v>320</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="G103" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H103" s="18">
+      <c r="G103" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" s="3">
         <v>419502402</v>
       </c>
-      <c r="I103" s="18" t="s">
+      <c r="I103" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="J103" s="19">
+      <c r="J103" s="13">
         <v>46142</v>
       </c>
-      <c r="K103" s="18">
+      <c r="K103" s="3">
         <v>60</v>
       </c>
-      <c r="L103" s="19">
-        <f>J103+K103</f>
+      <c r="L103" s="13">
+        <f t="shared" si="2"/>
         <v>46202</v>
       </c>
       <c r="M103" s="10">
         <v>46309</v>
       </c>
-      <c r="N103" s="20">
-        <f>M103-L103</f>
+      <c r="N103" s="18">
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O103" s="15">
@@ -8947,62 +8938,62 @@
       <c r="P103" s="15">
         <v>375000</v>
       </c>
-      <c r="Q103" s="22" t="s">
+      <c r="Q103" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R103" s="22" t="s">
+      <c r="R103" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S103" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T103" s="22" t="s">
+      <c r="S103" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T103" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="104" spans="1:20">
-      <c r="A104" s="18" t="s">
+      <c r="A104" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B104" s="18" t="s">
+      <c r="B104" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C104" s="18" t="s">
+      <c r="C104" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D104" s="18" t="s">
+      <c r="D104" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E104" s="18" t="s">
+      <c r="E104" s="3" t="s">
         <v>325</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G104" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H104" s="18" t="s">
+      <c r="G104" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H104" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="I104" s="18" t="s">
+      <c r="I104" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="J104" s="19">
+      <c r="J104" s="13">
         <v>46112</v>
       </c>
-      <c r="K104" s="21">
+      <c r="K104" s="14">
         <v>90</v>
       </c>
-      <c r="L104" s="19">
-        <f>J104+K104</f>
+      <c r="L104" s="13">
+        <f t="shared" si="2"/>
         <v>46202</v>
       </c>
       <c r="M104" s="10">
         <v>46309</v>
       </c>
-      <c r="N104" s="20">
-        <f>M104-L104</f>
+      <c r="N104" s="18">
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O104" s="15">
@@ -9011,62 +9002,62 @@
       <c r="P104" s="15">
         <v>475000</v>
       </c>
-      <c r="Q104" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R104" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S104" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T104" s="22" t="s">
+      <c r="Q104" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R104" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S104" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T104" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="105" spans="1:20">
-      <c r="A105" s="18" t="s">
+      <c r="A105" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="B105" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C105" s="18" t="s">
+      <c r="C105" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D105" s="18" t="s">
+      <c r="D105" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E105" s="18" t="s">
+      <c r="E105" s="3" t="s">
         <v>329</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="G105" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H105" s="18">
+      <c r="G105" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H105" s="3">
         <v>114404305</v>
       </c>
-      <c r="I105" s="18" t="s">
+      <c r="I105" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="J105" s="19">
+      <c r="J105" s="13">
         <v>46112</v>
       </c>
-      <c r="K105" s="21">
+      <c r="K105" s="14">
         <v>90</v>
       </c>
-      <c r="L105" s="19">
-        <f>J105+K105</f>
+      <c r="L105" s="13">
+        <f t="shared" si="2"/>
         <v>46202</v>
       </c>
       <c r="M105" s="10">
         <v>46309</v>
       </c>
-      <c r="N105" s="20">
-        <f>M105-L105</f>
+      <c r="N105" s="18">
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O105" s="15">
@@ -9075,62 +9066,62 @@
       <c r="P105" s="15">
         <v>495000</v>
       </c>
-      <c r="Q105" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R105" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S105" s="22" t="s">
+      <c r="Q105" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R105" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S105" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="T105" s="22" t="s">
+      <c r="T105" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="106" spans="1:20">
-      <c r="A106" s="18" t="s">
+      <c r="A106" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B106" s="18" t="s">
+      <c r="B106" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C106" s="18" t="s">
+      <c r="C106" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D106" s="18" t="s">
+      <c r="D106" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E106" s="18" t="s">
+      <c r="E106" s="3" t="s">
         <v>332</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="G106" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H106" s="18" t="s">
+      <c r="G106" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I106" s="18" t="s">
+      <c r="I106" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="J106" s="19">
+      <c r="J106" s="13">
         <v>46112</v>
       </c>
-      <c r="K106" s="21">
+      <c r="K106" s="14">
         <v>90</v>
       </c>
-      <c r="L106" s="19">
-        <f>J106+K106</f>
+      <c r="L106" s="13">
+        <f t="shared" si="2"/>
         <v>46202</v>
       </c>
       <c r="M106" s="10">
         <v>46309</v>
       </c>
-      <c r="N106" s="20">
-        <f>M106-L106</f>
+      <c r="N106" s="18">
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O106" s="15">
@@ -9139,62 +9130,62 @@
       <c r="P106" s="15">
         <v>550000</v>
       </c>
-      <c r="Q106" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R106" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S106" s="22" t="s">
+      <c r="Q106" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R106" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S106" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="T106" s="22" t="s">
+      <c r="T106" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="107" spans="1:20">
-      <c r="A107" s="18" t="s">
+      <c r="A107" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B107" s="18" t="s">
+      <c r="B107" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C107" s="18" t="s">
+      <c r="C107" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D107" s="18" t="s">
+      <c r="D107" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E107" s="18" t="s">
+      <c r="E107" s="3" t="s">
         <v>344</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="G107" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H107" s="18" t="s">
+      <c r="G107" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="I107" s="18" t="s">
+      <c r="I107" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="J107" s="19">
+      <c r="J107" s="13">
         <v>46142</v>
       </c>
-      <c r="K107" s="18">
+      <c r="K107" s="3">
         <v>60</v>
       </c>
-      <c r="L107" s="19">
-        <f>J107+K107</f>
+      <c r="L107" s="13">
+        <f t="shared" si="2"/>
         <v>46202</v>
       </c>
       <c r="M107" s="10">
         <v>46309</v>
       </c>
-      <c r="N107" s="20">
-        <f>M107-L107</f>
+      <c r="N107" s="18">
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O107" s="15">
@@ -9203,62 +9194,62 @@
       <c r="P107" s="15">
         <v>475000</v>
       </c>
-      <c r="Q107" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R107" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S107" s="22" t="s">
+      <c r="Q107" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R107" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S107" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="T107" s="22" t="s">
+      <c r="T107" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="108" spans="1:20">
-      <c r="A108" s="18" t="s">
+      <c r="A108" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="B108" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D108" s="18" t="s">
+      <c r="D108" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E108" s="18" t="s">
+      <c r="E108" s="3" t="s">
         <v>348</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="G108" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H108" s="18">
+      <c r="G108" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H108" s="3">
         <v>661101038</v>
       </c>
-      <c r="I108" s="18" t="s">
+      <c r="I108" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="J108" s="19">
+      <c r="J108" s="13">
         <v>46112</v>
       </c>
-      <c r="K108" s="21">
+      <c r="K108" s="14">
         <v>90</v>
       </c>
-      <c r="L108" s="19">
-        <f>J108+K108</f>
+      <c r="L108" s="13">
+        <f t="shared" si="2"/>
         <v>46202</v>
       </c>
       <c r="M108" s="10">
         <v>46309</v>
       </c>
-      <c r="N108" s="20">
-        <f>M108-L108</f>
+      <c r="N108" s="18">
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O108" s="15">
@@ -9267,62 +9258,62 @@
       <c r="P108" s="15">
         <v>495000</v>
       </c>
-      <c r="Q108" s="22" t="s">
+      <c r="Q108" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R108" s="22" t="s">
+      <c r="R108" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S108" s="22" t="s">
+      <c r="S108" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T108" s="22" t="s">
+      <c r="T108" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="109" spans="1:20">
-      <c r="A109" s="18" t="s">
+      <c r="A109" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B109" s="18" t="s">
+      <c r="B109" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C109" s="18" t="s">
+      <c r="C109" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D109" s="18" t="s">
+      <c r="D109" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E109" s="18" t="s">
+      <c r="E109" s="3" t="s">
         <v>359</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G109" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H109" s="18" t="s">
+      <c r="G109" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="I109" s="18" t="s">
+      <c r="I109" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="J109" s="19">
+      <c r="J109" s="13">
         <v>46112</v>
       </c>
-      <c r="K109" s="21">
+      <c r="K109" s="14">
         <v>90</v>
       </c>
-      <c r="L109" s="19">
-        <f>J109+K109</f>
+      <c r="L109" s="13">
+        <f t="shared" si="2"/>
         <v>46202</v>
       </c>
       <c r="M109" s="10">
         <v>46309</v>
       </c>
-      <c r="N109" s="20">
-        <f>M109-L109</f>
+      <c r="N109" s="18">
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O109" s="15">
@@ -9331,62 +9322,62 @@
       <c r="P109" s="15">
         <v>495000</v>
       </c>
-      <c r="Q109" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R109" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S109" s="22" t="s">
+      <c r="Q109" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R109" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S109" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="T109" s="22" t="s">
+      <c r="T109" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="110" spans="1:20">
-      <c r="A110" s="18" t="s">
+      <c r="A110" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B110" s="18" t="s">
+      <c r="B110" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C110" s="18" t="s">
+      <c r="C110" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="D110" s="18" t="s">
+      <c r="D110" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E110" s="18" t="s">
+      <c r="E110" s="3" t="s">
         <v>313</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="G110" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H110" s="18" t="s">
+      <c r="G110" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="I110" s="18" t="s">
+      <c r="I110" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="J110" s="19">
+      <c r="J110" s="13">
         <v>46111</v>
       </c>
-      <c r="K110" s="21">
+      <c r="K110" s="14">
         <v>90</v>
       </c>
-      <c r="L110" s="19">
-        <f>J110+K110</f>
+      <c r="L110" s="13">
+        <f t="shared" si="2"/>
         <v>46201</v>
       </c>
       <c r="M110" s="10">
         <v>46309</v>
       </c>
-      <c r="N110" s="20">
-        <f>M110-L110</f>
+      <c r="N110" s="18">
+        <f t="shared" si="3"/>
         <v>108</v>
       </c>
       <c r="O110" s="15">
@@ -9395,62 +9386,62 @@
       <c r="P110" s="15">
         <v>550000</v>
       </c>
-      <c r="Q110" s="22" t="s">
+      <c r="Q110" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R110" s="22" t="s">
+      <c r="R110" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S110" s="22" t="s">
+      <c r="S110" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="T110" s="22" t="s">
+      <c r="T110" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="111" spans="1:20">
-      <c r="A111" s="18" t="s">
+      <c r="A111" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B111" s="18" t="s">
+      <c r="B111" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C111" s="18" t="s">
+      <c r="C111" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D111" s="18" t="s">
+      <c r="D111" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E111" s="18" t="s">
+      <c r="E111" s="3" t="s">
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G111" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H111" s="18" t="s">
+      <c r="G111" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I111" s="18" t="s">
+      <c r="I111" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J111" s="19">
+      <c r="J111" s="13">
         <v>46112</v>
       </c>
-      <c r="K111" s="21">
+      <c r="K111" s="14">
         <v>60</v>
       </c>
-      <c r="L111" s="19">
-        <f>J111+K111</f>
+      <c r="L111" s="13">
+        <f t="shared" si="2"/>
         <v>46172</v>
       </c>
       <c r="M111" s="10">
         <v>46309</v>
       </c>
-      <c r="N111" s="20">
-        <f>M111-L111</f>
+      <c r="N111" s="18">
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O111" s="15">
@@ -9459,62 +9450,62 @@
       <c r="P111" s="15">
         <v>475000</v>
       </c>
-      <c r="Q111" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R111" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S111" s="22" t="s">
+      <c r="Q111" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R111" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S111" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="T111" s="22" t="s">
+      <c r="T111" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="112" spans="1:20">
-      <c r="A112" s="18" t="s">
+      <c r="A112" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B112" s="18" t="s">
+      <c r="B112" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C112" s="18" t="s">
+      <c r="C112" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D112" s="18" t="s">
+      <c r="D112" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E112" s="18" t="s">
+      <c r="E112" s="3" t="s">
         <v>247</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="G112" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H112" s="18" t="s">
+      <c r="G112" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I112" s="18" t="s">
+      <c r="I112" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="J112" s="19">
+      <c r="J112" s="13">
         <v>46112</v>
       </c>
-      <c r="K112" s="21">
+      <c r="K112" s="14">
         <v>60</v>
       </c>
-      <c r="L112" s="19">
-        <f>J112+K112</f>
+      <c r="L112" s="13">
+        <f t="shared" si="2"/>
         <v>46172</v>
       </c>
       <c r="M112" s="10">
         <v>46309</v>
       </c>
-      <c r="N112" s="20">
-        <f>M112-L112</f>
+      <c r="N112" s="18">
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O112" s="15">
@@ -9523,62 +9514,62 @@
       <c r="P112" s="15">
         <v>375000</v>
       </c>
-      <c r="Q112" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R112" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S112" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T112" s="22" t="s">
+      <c r="Q112" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R112" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S112" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T112" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="113" spans="1:20">
-      <c r="A113" s="18" t="s">
+      <c r="A113" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B113" s="18" t="s">
+      <c r="B113" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C113" s="18" t="s">
+      <c r="C113" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D113" s="18" t="s">
+      <c r="D113" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E113" s="18" t="s">
+      <c r="E113" s="3" t="s">
         <v>253</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G113" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H113" s="18">
+      <c r="G113" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" s="3">
         <v>679004406</v>
       </c>
-      <c r="I113" s="18" t="s">
+      <c r="I113" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="J113" s="19">
+      <c r="J113" s="13">
         <v>46112</v>
       </c>
-      <c r="K113" s="21">
+      <c r="K113" s="14">
         <v>60</v>
       </c>
-      <c r="L113" s="19">
-        <f>J113+K113</f>
+      <c r="L113" s="13">
+        <f t="shared" si="2"/>
         <v>46172</v>
       </c>
       <c r="M113" s="10">
         <v>46309</v>
       </c>
-      <c r="N113" s="20">
-        <f>M113-L113</f>
+      <c r="N113" s="18">
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O113" s="15">
@@ -9587,62 +9578,62 @@
       <c r="P113" s="15">
         <v>475000</v>
       </c>
-      <c r="Q113" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R113" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S113" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T113" s="22" t="s">
+      <c r="Q113" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R113" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S113" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T113" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="114" spans="1:20">
-      <c r="A114" s="18" t="s">
+      <c r="A114" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B114" s="18" t="s">
+      <c r="B114" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C114" s="18" t="s">
+      <c r="C114" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D114" s="18" t="s">
+      <c r="D114" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E114" s="18" t="s">
+      <c r="E114" s="3" t="s">
         <v>256</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="G114" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H114" s="18" t="s">
+      <c r="G114" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I114" s="18" t="s">
+      <c r="I114" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="J114" s="19">
+      <c r="J114" s="13">
         <v>46112</v>
       </c>
-      <c r="K114" s="21">
+      <c r="K114" s="14">
         <v>60</v>
       </c>
-      <c r="L114" s="19">
-        <f>J114+K114</f>
+      <c r="L114" s="13">
+        <f t="shared" si="2"/>
         <v>46172</v>
       </c>
       <c r="M114" s="10">
         <v>46309</v>
       </c>
-      <c r="N114" s="20">
-        <f>M114-L114</f>
+      <c r="N114" s="18">
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O114" s="15">
@@ -9651,62 +9642,62 @@
       <c r="P114" s="15">
         <v>325000</v>
       </c>
-      <c r="Q114" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R114" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S114" s="22" t="s">
+      <c r="Q114" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R114" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S114" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="T114" s="22" t="s">
+      <c r="T114" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="115" spans="1:20">
-      <c r="A115" s="18" t="s">
+      <c r="A115" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B115" s="18" t="s">
+      <c r="B115" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C115" s="18" t="s">
+      <c r="C115" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D115" s="18" t="s">
+      <c r="D115" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E115" s="18" t="s">
+      <c r="E115" s="3" t="s">
         <v>260</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="G115" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H115" s="18" t="s">
+      <c r="G115" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="I115" s="18" t="s">
+      <c r="I115" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J115" s="19">
+      <c r="J115" s="13">
         <v>46112</v>
       </c>
-      <c r="K115" s="21">
+      <c r="K115" s="14">
         <v>60</v>
       </c>
-      <c r="L115" s="19">
-        <f>J115+K115</f>
+      <c r="L115" s="13">
+        <f t="shared" si="2"/>
         <v>46172</v>
       </c>
       <c r="M115" s="10">
         <v>46309</v>
       </c>
-      <c r="N115" s="20">
-        <f>M115-L115</f>
+      <c r="N115" s="18">
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O115" s="15">
@@ -9715,62 +9706,62 @@
       <c r="P115" s="15">
         <v>375000</v>
       </c>
-      <c r="Q115" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R115" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S115" s="22" t="s">
+      <c r="Q115" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R115" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S115" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T115" s="22" t="s">
+      <c r="T115" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="116" spans="1:20">
-      <c r="A116" s="18" t="s">
+      <c r="A116" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B116" s="18" t="s">
+      <c r="B116" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C116" s="18" t="s">
+      <c r="C116" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D116" s="18" t="s">
+      <c r="D116" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E116" s="18" t="s">
+      <c r="E116" s="3" t="s">
         <v>264</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G116" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H116" s="18">
+      <c r="G116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" s="3">
         <v>6478802340</v>
       </c>
-      <c r="I116" s="18" t="s">
+      <c r="I116" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="J116" s="19">
+      <c r="J116" s="13">
         <v>46112</v>
       </c>
-      <c r="K116" s="21">
+      <c r="K116" s="14">
         <v>60</v>
       </c>
-      <c r="L116" s="19">
-        <f>J116+K116</f>
+      <c r="L116" s="13">
+        <f t="shared" si="2"/>
         <v>46172</v>
       </c>
       <c r="M116" s="10">
         <v>46309</v>
       </c>
-      <c r="N116" s="20">
-        <f>M116-L116</f>
+      <c r="N116" s="18">
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O116" s="15">
@@ -9779,62 +9770,62 @@
       <c r="P116" s="15">
         <v>385000</v>
       </c>
-      <c r="Q116" s="22" t="s">
+      <c r="Q116" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="R116" s="22" t="s">
+      <c r="R116" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="S116" s="22" t="s">
+      <c r="S116" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T116" s="22" t="s">
+      <c r="T116" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="117" spans="1:20">
-      <c r="A117" s="18" t="s">
+      <c r="A117" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C117" s="18" t="s">
+      <c r="C117" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D117" s="18" t="s">
+      <c r="D117" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E117" s="18" t="s">
+      <c r="E117" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="G117" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H117" s="18">
+      <c r="G117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H117" s="3">
         <v>5012804793</v>
       </c>
-      <c r="I117" s="18" t="s">
+      <c r="I117" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J117" s="19">
+      <c r="J117" s="13">
         <v>46142</v>
       </c>
-      <c r="K117" s="18">
+      <c r="K117" s="3">
         <v>30</v>
       </c>
-      <c r="L117" s="19">
-        <f>J117+K117</f>
+      <c r="L117" s="13">
+        <f t="shared" si="2"/>
         <v>46172</v>
       </c>
       <c r="M117" s="10">
         <v>46309</v>
       </c>
-      <c r="N117" s="20">
-        <f>M117-L117</f>
+      <c r="N117" s="18">
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O117" s="15">
@@ -9843,62 +9834,62 @@
       <c r="P117" s="15">
         <v>475000</v>
       </c>
-      <c r="Q117" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R117" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S117" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T117" s="22" t="s">
+      <c r="Q117" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R117" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S117" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T117" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="118" spans="1:20">
-      <c r="A118" s="18" t="s">
+      <c r="A118" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B118" s="18" t="s">
+      <c r="B118" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C118" s="18" t="s">
+      <c r="C118" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D118" s="18" t="s">
+      <c r="D118" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E118" s="18" t="s">
+      <c r="E118" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G118" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H118" s="18" t="s">
+      <c r="G118" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I118" s="18" t="s">
+      <c r="I118" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="J118" s="19">
+      <c r="J118" s="13">
         <v>46111</v>
       </c>
-      <c r="K118" s="21">
+      <c r="K118" s="14">
         <v>60</v>
       </c>
-      <c r="L118" s="19">
-        <f>J118+K118</f>
+      <c r="L118" s="13">
+        <f t="shared" si="2"/>
         <v>46171</v>
       </c>
       <c r="M118" s="10">
         <v>46309</v>
       </c>
-      <c r="N118" s="20">
-        <f>M118-L118</f>
+      <c r="N118" s="18">
+        <f t="shared" si="3"/>
         <v>138</v>
       </c>
       <c r="O118" s="15">
@@ -9907,62 +9898,62 @@
       <c r="P118" s="15">
         <v>550000</v>
       </c>
-      <c r="Q118" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="R118" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="S118" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T118" s="22" t="s">
+      <c r="Q118" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R118" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="S118" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T118" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="119" spans="1:20">
-      <c r="A119" s="18" t="s">
+      <c r="A119" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B119" s="18" t="s">
+      <c r="B119" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C119" s="18" t="s">
+      <c r="C119" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D119" s="18" t="s">
+      <c r="D119" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E119" s="18" t="s">
+      <c r="E119" s="3" t="s">
         <v>219</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G119" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H119" s="18">
+      <c r="G119" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" s="3">
         <v>70602147</v>
       </c>
-      <c r="I119" s="18" t="s">
+      <c r="I119" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="J119" s="19">
+      <c r="J119" s="13">
         <v>46111</v>
       </c>
-      <c r="K119" s="21">
+      <c r="K119" s="14">
         <v>60</v>
       </c>
-      <c r="L119" s="19">
-        <f>J119+K119</f>
+      <c r="L119" s="13">
+        <f t="shared" si="2"/>
         <v>46171</v>
       </c>
       <c r="M119" s="10">
         <v>46309</v>
       </c>
-      <c r="N119" s="20">
-        <f>M119-L119</f>
+      <c r="N119" s="18">
+        <f t="shared" si="3"/>
         <v>138</v>
       </c>
       <c r="O119" s="15">
@@ -9971,62 +9962,62 @@
       <c r="P119" s="15">
         <v>245000</v>
       </c>
-      <c r="Q119" s="22" t="s">
+      <c r="Q119" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R119" s="22" t="s">
+      <c r="R119" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S119" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T119" s="22" t="s">
+      <c r="S119" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T119" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="120" spans="1:20">
-      <c r="A120" s="18" t="s">
+      <c r="A120" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B120" s="18" t="s">
+      <c r="B120" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C120" s="18" t="s">
+      <c r="C120" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D120" s="18" t="s">
+      <c r="D120" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E120" s="18" t="s">
+      <c r="E120" s="3" t="s">
         <v>185</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G120" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H120" s="18" t="s">
+      <c r="G120" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I120" s="18" t="s">
+      <c r="I120" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J120" s="19">
+      <c r="J120" s="13">
         <v>46109</v>
       </c>
-      <c r="K120" s="21">
+      <c r="K120" s="14">
         <v>60</v>
       </c>
-      <c r="L120" s="19">
-        <f>J120+K120</f>
+      <c r="L120" s="13">
+        <f t="shared" si="2"/>
         <v>46169</v>
       </c>
       <c r="M120" s="10">
         <v>46309</v>
       </c>
-      <c r="N120" s="20">
-        <f>M120-L120</f>
+      <c r="N120" s="18">
+        <f t="shared" si="3"/>
         <v>140</v>
       </c>
       <c r="O120" s="15">
@@ -10035,62 +10026,62 @@
       <c r="P120" s="15">
         <v>495000</v>
       </c>
-      <c r="Q120" s="22" t="s">
+      <c r="Q120" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R120" s="22" t="s">
+      <c r="R120" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S120" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="T120" s="22" t="s">
+      <c r="S120" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="T120" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="121" spans="1:20">
-      <c r="A121" s="18" t="s">
+      <c r="A121" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B121" s="18" t="s">
+      <c r="B121" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C121" s="18" t="s">
+      <c r="C121" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D121" s="18" t="s">
+      <c r="D121" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E121" s="18" t="s">
+      <c r="E121" s="3" t="s">
         <v>177</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G121" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H121" s="18" t="s">
+      <c r="G121" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I121" s="18" t="s">
+      <c r="I121" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J121" s="19">
+      <c r="J121" s="13">
         <v>46106</v>
       </c>
-      <c r="K121" s="21">
+      <c r="K121" s="14">
         <v>60</v>
       </c>
-      <c r="L121" s="19">
-        <f>J121+K121</f>
+      <c r="L121" s="13">
+        <f t="shared" si="2"/>
         <v>46166</v>
       </c>
       <c r="M121" s="10">
         <v>46309</v>
       </c>
-      <c r="N121" s="20">
-        <f>M121-L121</f>
+      <c r="N121" s="18">
+        <f t="shared" si="3"/>
         <v>143</v>
       </c>
       <c r="O121" s="15">
@@ -10099,62 +10090,62 @@
       <c r="P121" s="15">
         <v>375000</v>
       </c>
-      <c r="Q121" s="22" t="s">
+      <c r="Q121" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R121" s="22" t="s">
+      <c r="R121" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S121" s="22" t="s">
+      <c r="S121" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="T121" s="22" t="s">
+      <c r="T121" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="122" spans="1:20">
-      <c r="A122" s="18" t="s">
+      <c r="A122" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B122" s="18" t="s">
+      <c r="B122" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C122" s="18" t="s">
+      <c r="C122" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D122" s="18" t="s">
+      <c r="D122" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E122" s="18" t="s">
+      <c r="E122" s="3" t="s">
         <v>158</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G122" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H122" s="18" t="s">
+      <c r="G122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H122" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I122" s="18" t="s">
+      <c r="I122" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J122" s="19">
+      <c r="J122" s="13">
         <v>46053</v>
       </c>
-      <c r="K122" s="21">
+      <c r="K122" s="14">
         <v>90</v>
       </c>
-      <c r="L122" s="19">
-        <f>J122+K122</f>
+      <c r="L122" s="13">
+        <f t="shared" si="2"/>
         <v>46143</v>
       </c>
       <c r="M122" s="10">
         <v>46309</v>
       </c>
-      <c r="N122" s="20">
-        <f>M122-L122</f>
+      <c r="N122" s="18">
+        <f t="shared" si="3"/>
         <v>166</v>
       </c>
       <c r="O122" s="15">
@@ -10163,16 +10154,16 @@
       <c r="P122" s="15">
         <v>495000</v>
       </c>
-      <c r="Q122" s="22" t="s">
+      <c r="Q122" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="R122" s="22" t="s">
+      <c r="R122" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S122" s="22" t="s">
+      <c r="S122" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T122" s="22" t="s">
+      <c r="T122" s="19" t="s">
         <v>92</v>
       </c>
     </row>
@@ -10181,8 +10172,8 @@
     <cfRule type="duplicateValues" dxfId="44" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E66">
-    <cfRule type="duplicateValues" dxfId="43" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E74">
     <cfRule type="duplicateValues" dxfId="41" priority="35"/>
@@ -10191,8 +10182,8 @@
     <cfRule type="duplicateValues" dxfId="40" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E80">
-    <cfRule type="duplicateValues" dxfId="39" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61:E62">
     <cfRule type="duplicateValues" dxfId="37" priority="44"/>
@@ -10230,50 +10221,50 @@
   <conditionalFormatting sqref="E79:E80">
     <cfRule type="duplicateValues" dxfId="26" priority="40"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E81:E92">
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E81:E95">
+    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E81:E120">
+    <cfRule type="duplicateValues" dxfId="23" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E93">
-    <cfRule type="duplicateValues" dxfId="25" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="25" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E94:E95">
-    <cfRule type="duplicateValues" dxfId="24" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="23" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96:E99">
-    <cfRule type="duplicateValues" dxfId="22" priority="20" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E100:E104">
-    <cfRule type="duplicateValues" dxfId="21" priority="18" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="18" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E105:E106">
-    <cfRule type="duplicateValues" dxfId="20" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107:E113">
-    <cfRule type="duplicateValues" dxfId="19" priority="12" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="14" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="12" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E114:E117">
-    <cfRule type="duplicateValues" dxfId="17" priority="9" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="11" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="11" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E118:E120">
-    <cfRule type="duplicateValues" dxfId="15" priority="6" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E121">
-    <cfRule type="duplicateValues" dxfId="13" priority="3" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="4" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E122">
-    <cfRule type="duplicateValues" dxfId="11" priority="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E81:E92">
-    <cfRule type="duplicateValues" dxfId="9" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E81:E95">
-    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E81:E120">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H94:H95">
     <cfRule type="duplicateValues" dxfId="6" priority="22" stopIfTrue="1"/>

--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/UNPAID AND OVERDUE CREDIT SALES - BIKES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="387" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{776F6ABE-EC9D-4425-AEE4-EAC89C4168D5}"/>
+  <xr:revisionPtr revIDLastSave="411" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8C17EEB-0367-4548-AA22-F0226329A56F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1523,12 +1523,19 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1621,49 +1628,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1671,17 +1663,35 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1694,701 +1704,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="121">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="44">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2814,28 +2130,16 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3124,16 +2428,16 @@
     <col min="4" max="4" width="15.90625" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="9.453125" customWidth="1"/>
-    <col min="11" max="11" width="6.54296875" customWidth="1"/>
-    <col min="12" max="12" width="9.36328125" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" customWidth="1"/>
-    <col min="14" max="14" width="8.1796875" customWidth="1"/>
-    <col min="15" max="15" width="13.453125" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="40" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="6.54296875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="9.36328125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7265625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7265625" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="40.1796875" customWidth="1"/>
     <col min="18" max="18" width="38.08984375" customWidth="1"/>
     <col min="19" max="19" width="27.6328125" bestFit="1" customWidth="1"/>
@@ -3244,7 +2548,7 @@
         <v>46309</v>
       </c>
       <c r="N2" s="18">
-        <f>M2-L2</f>
+        <f t="shared" ref="N2:N33" si="0">M2-L2</f>
         <v>137</v>
       </c>
       <c r="O2" s="15">
@@ -3260,7 +2564,7 @@
         <v>39</v>
       </c>
       <c r="S2" s="16" t="s">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="T2" s="16" t="s">
         <v>92</v>
@@ -3307,7 +2611,7 @@
         <v>46309</v>
       </c>
       <c r="N3" s="18">
-        <f>M3-L3</f>
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="O3" s="15">
@@ -3370,7 +2674,7 @@
         <v>46309</v>
       </c>
       <c r="N4" s="18">
-        <f>M4-L4</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="O4" s="12">
@@ -3433,7 +2737,7 @@
         <v>46309</v>
       </c>
       <c r="N5" s="18">
-        <f>M5-L5</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="O5" s="15">
@@ -3497,7 +2801,7 @@
         <v>46309</v>
       </c>
       <c r="N6" s="18">
-        <f>M6-L6</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="O6" s="15">
@@ -3561,7 +2865,7 @@
         <v>46309</v>
       </c>
       <c r="N7" s="18">
-        <f>M7-L7</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="O7" s="15">
@@ -3570,14 +2874,14 @@
       <c r="P7" s="15">
         <v>495000</v>
       </c>
-      <c r="Q7" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="R7" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="S7" s="19" t="s">
-        <v>236</v>
+      <c r="Q7" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="R7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="T7" s="19" t="s">
         <v>92</v>
@@ -3624,7 +2928,7 @@
         <v>46309</v>
       </c>
       <c r="N8" s="18">
-        <f>M8-L8</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="O8" s="15">
@@ -3687,7 +2991,7 @@
         <v>46309</v>
       </c>
       <c r="N9" s="18">
-        <f>M9-L9</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="O9" s="15">
@@ -3750,7 +3054,7 @@
         <v>46309</v>
       </c>
       <c r="N10" s="18">
-        <f>M10-L10</f>
+        <f t="shared" si="0"/>
         <v>140</v>
       </c>
       <c r="O10" s="15">
@@ -3813,7 +3117,7 @@
         <v>46309</v>
       </c>
       <c r="N11" s="18">
-        <f>M11-L11</f>
+        <f t="shared" si="0"/>
         <v>138</v>
       </c>
       <c r="O11" s="15">
@@ -3876,7 +3180,7 @@
         <v>46309</v>
       </c>
       <c r="N12" s="18">
-        <f>M12-L12</f>
+        <f t="shared" si="0"/>
         <v>138</v>
       </c>
       <c r="O12" s="15">
@@ -3939,7 +3243,7 @@
         <v>46309</v>
       </c>
       <c r="N13" s="18">
-        <f>M13-L13</f>
+        <f t="shared" si="0"/>
         <v>138</v>
       </c>
       <c r="O13" s="15">
@@ -4002,7 +3306,7 @@
         <v>46309</v>
       </c>
       <c r="N14" s="18">
-        <f>M14-L14</f>
+        <f t="shared" si="0"/>
         <v>138</v>
       </c>
       <c r="O14" s="15">
@@ -4065,7 +3369,7 @@
         <v>46309</v>
       </c>
       <c r="N15" s="18">
-        <f>M15-L15</f>
+        <f t="shared" si="0"/>
         <v>140</v>
       </c>
       <c r="O15" s="15">
@@ -4128,7 +3432,7 @@
         <v>46309</v>
       </c>
       <c r="N16" s="18">
-        <f>M16-L16</f>
+        <f t="shared" si="0"/>
         <v>115</v>
       </c>
       <c r="O16" s="12">
@@ -4191,7 +3495,7 @@
         <v>46309</v>
       </c>
       <c r="N17" s="18">
-        <f>M17-L17</f>
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="O17" s="11">
@@ -4254,7 +3558,7 @@
         <v>46309</v>
       </c>
       <c r="N18" s="18">
-        <f>M18-L18</f>
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
       <c r="O18" s="15">
@@ -4317,7 +3621,7 @@
         <v>46309</v>
       </c>
       <c r="N19" s="18">
-        <f>M19-L19</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="O19" s="11">
@@ -4380,7 +3684,7 @@
         <v>46309</v>
       </c>
       <c r="N20" s="18">
-        <f>M20-L20</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="O20" s="11">
@@ -4443,7 +3747,7 @@
         <v>46309</v>
       </c>
       <c r="N21" s="18">
-        <f>M21-L21</f>
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
       <c r="O21" s="15">
@@ -4507,7 +3811,7 @@
         <v>46309</v>
       </c>
       <c r="N22" s="18">
-        <f>M22-L22</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="O22" s="15">
@@ -4570,7 +3874,7 @@
         <v>46309</v>
       </c>
       <c r="N23" s="18">
-        <f>M23-L23</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="O23" s="12">
@@ -4634,7 +3938,7 @@
         <v>46309</v>
       </c>
       <c r="N24" s="18">
-        <f>M24-L24</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="O24" s="15">
@@ -4698,7 +4002,7 @@
         <v>46309</v>
       </c>
       <c r="N25" s="18">
-        <f>M25-L25</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="O25" s="15">
@@ -4761,7 +4065,7 @@
         <v>46309</v>
       </c>
       <c r="N26" s="18">
-        <f>M26-L26</f>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="O26" s="15">
@@ -4824,7 +4128,7 @@
         <v>46309</v>
       </c>
       <c r="N27" s="18">
-        <f>M27-L27</f>
+        <f t="shared" si="0"/>
         <v>110</v>
       </c>
       <c r="O27" s="15">
@@ -4887,7 +4191,7 @@
         <v>46309</v>
       </c>
       <c r="N28" s="18">
-        <f>M28-L28</f>
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
       <c r="O28" s="15">
@@ -4950,7 +4254,7 @@
         <v>46309</v>
       </c>
       <c r="N29" s="18">
-        <f>M29-L29</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="O29" s="15">
@@ -5014,7 +4318,7 @@
         <v>46309</v>
       </c>
       <c r="N30" s="18">
-        <f>M30-L30</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="O30" s="15">
@@ -5077,7 +4381,7 @@
         <v>46309</v>
       </c>
       <c r="N31" s="18">
-        <f>M31-L31</f>
+        <f t="shared" si="0"/>
         <v>138</v>
       </c>
       <c r="O31" s="15">
@@ -5140,7 +4444,7 @@
         <v>46309</v>
       </c>
       <c r="N32" s="18">
-        <f>M32-L32</f>
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
       <c r="O32" s="15">
@@ -5156,7 +4460,7 @@
         <v>39</v>
       </c>
       <c r="S32" s="16" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="T32" s="16" t="s">
         <v>92</v>
@@ -5197,14 +4501,14 @@
         <v>90</v>
       </c>
       <c r="L33" s="13">
-        <f>J33+K33</f>
+        <f t="shared" ref="L33:L38" si="1">J33+K33</f>
         <v>46202</v>
       </c>
       <c r="M33" s="10">
         <v>46309</v>
       </c>
       <c r="N33" s="18">
-        <f>M33-L33</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="O33" s="15">
@@ -5219,8 +4523,8 @@
       <c r="R33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="S33" s="20" t="s">
-        <v>236</v>
+      <c r="S33" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="T33" s="19" t="s">
         <v>92</v>
@@ -5261,14 +4565,14 @@
         <v>90</v>
       </c>
       <c r="L34" s="13">
-        <f>J34+K34</f>
+        <f t="shared" si="1"/>
         <v>46202</v>
       </c>
       <c r="M34" s="10">
         <v>46309</v>
       </c>
       <c r="N34" s="18">
-        <f>M34-L34</f>
+        <f t="shared" ref="N34:N65" si="2">M34-L34</f>
         <v>107</v>
       </c>
       <c r="O34" s="15">
@@ -5283,8 +4587,8 @@
       <c r="R34" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="S34" s="19" t="s">
-        <v>236</v>
+      <c r="S34" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="T34" s="19" t="s">
         <v>92</v>
@@ -5325,14 +4629,14 @@
         <v>90</v>
       </c>
       <c r="L35" s="13">
-        <f>J35+K35</f>
+        <f t="shared" si="1"/>
         <v>46202</v>
       </c>
       <c r="M35" s="10">
         <v>46309</v>
       </c>
       <c r="N35" s="18">
-        <f>M35-L35</f>
+        <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="O35" s="15">
@@ -5347,8 +4651,8 @@
       <c r="R35" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="S35" s="19" t="s">
-        <v>236</v>
+      <c r="S35" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="T35" s="19" t="s">
         <v>92</v>
@@ -5389,14 +4693,14 @@
         <v>60</v>
       </c>
       <c r="L36" s="13">
-        <f>J36+K36</f>
+        <f t="shared" si="1"/>
         <v>46291</v>
       </c>
       <c r="M36" s="10">
         <v>46309</v>
       </c>
       <c r="N36" s="18">
-        <f>M36-L36</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="O36" s="15">
@@ -5411,11 +4715,11 @@
       <c r="R36" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S36" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="T36" s="19" t="s">
-        <v>92</v>
+      <c r="S36" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="T36" s="21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -5453,14 +4757,14 @@
         <v>60</v>
       </c>
       <c r="L37" s="13">
-        <f>J37+K37</f>
+        <f t="shared" si="1"/>
         <v>46294</v>
       </c>
       <c r="M37" s="10">
         <v>46309</v>
       </c>
       <c r="N37" s="18">
-        <f>M37-L37</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O37" s="15">
@@ -5517,14 +4821,14 @@
         <v>60</v>
       </c>
       <c r="L38" s="13">
-        <f>J38+K38</f>
+        <f t="shared" si="1"/>
         <v>46172</v>
       </c>
       <c r="M38" s="10">
         <v>46309</v>
       </c>
       <c r="N38" s="18">
-        <f>M38-L38</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="O38" s="15">
@@ -5539,8 +4843,8 @@
       <c r="R38" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="S38" s="19" t="s">
-        <v>236</v>
+      <c r="S38" s="21" t="s">
+        <v>29</v>
       </c>
       <c r="T38" s="19" t="s">
         <v>92</v>
@@ -5587,7 +4891,7 @@
         <v>46309</v>
       </c>
       <c r="N39" s="18">
-        <f>M39-L39</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="O39" s="15">
@@ -5650,7 +4954,7 @@
         <v>46309</v>
       </c>
       <c r="N40" s="18">
-        <f>M40-L40</f>
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="O40" s="15">
@@ -5713,7 +5017,7 @@
         <v>46309</v>
       </c>
       <c r="N41" s="18">
-        <f>M41-L41</f>
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="O41" s="15">
@@ -5776,7 +5080,7 @@
         <v>46309</v>
       </c>
       <c r="N42" s="18">
-        <f>M42-L42</f>
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="O42" s="15">
@@ -5840,7 +5144,7 @@
         <v>46309</v>
       </c>
       <c r="N43" s="18">
-        <f>M43-L43</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="O43" s="15">
@@ -5855,8 +5159,8 @@
       <c r="R43" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="S43" s="19" t="s">
-        <v>29</v>
+      <c r="S43" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="T43" s="19" t="s">
         <v>92</v>
@@ -5904,7 +5208,7 @@
         <v>46309</v>
       </c>
       <c r="N44" s="18">
-        <f>M44-L44</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="O44" s="15">
@@ -5967,7 +5271,7 @@
         <v>46309</v>
       </c>
       <c r="N45" s="18">
-        <f>M45-L45</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="O45" s="15">
@@ -6030,7 +5334,7 @@
         <v>46309</v>
       </c>
       <c r="N46" s="18">
-        <f>M46-L46</f>
+        <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="O46" s="15">
@@ -6093,7 +5397,7 @@
         <v>46309</v>
       </c>
       <c r="N47" s="18">
-        <f>M47-L47</f>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="O47" s="15">
@@ -6156,7 +5460,7 @@
         <v>46309</v>
       </c>
       <c r="N48" s="18">
-        <f>M48-L48</f>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="O48" s="11">
@@ -6219,7 +5523,7 @@
         <v>46309</v>
       </c>
       <c r="N49" s="18">
-        <f>M49-L49</f>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="O49" s="15">
@@ -6282,7 +5586,7 @@
         <v>46309</v>
       </c>
       <c r="N50" s="18">
-        <f>M50-L50</f>
+        <f t="shared" si="2"/>
         <v>108</v>
       </c>
       <c r="O50" s="12">
@@ -6345,7 +5649,7 @@
         <v>46309</v>
       </c>
       <c r="N51" s="18">
-        <f>M51-L51</f>
+        <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="O51" s="15">
@@ -6408,7 +5712,7 @@
         <v>46309</v>
       </c>
       <c r="N52" s="18">
-        <f>M52-L52</f>
+        <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="O52" s="15">
@@ -6471,7 +5775,7 @@
         <v>46309</v>
       </c>
       <c r="N53" s="18">
-        <f>M53-L53</f>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="O53" s="11">
@@ -6534,7 +5838,7 @@
         <v>46309</v>
       </c>
       <c r="N54" s="18">
-        <f>M54-L54</f>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="O54" s="11">
@@ -6597,7 +5901,7 @@
         <v>46309</v>
       </c>
       <c r="N55" s="18">
-        <f>M55-L55</f>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="O55" s="11">
@@ -6660,7 +5964,7 @@
         <v>46309</v>
       </c>
       <c r="N56" s="18">
-        <f>M56-L56</f>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="O56" s="11">
@@ -6723,7 +6027,7 @@
         <v>46309</v>
       </c>
       <c r="N57" s="18">
-        <f>M57-L57</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="O57" s="15">
@@ -6786,7 +6090,7 @@
         <v>46309</v>
       </c>
       <c r="N58" s="18">
-        <f>M58-L58</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="O58" s="15">
@@ -6849,7 +6153,7 @@
         <v>46309</v>
       </c>
       <c r="N59" s="18">
-        <f>M59-L59</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="O59" s="15">
@@ -6912,7 +6216,7 @@
         <v>46309</v>
       </c>
       <c r="N60" s="18">
-        <f>M60-L60</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="O60" s="15">
@@ -6931,7 +6235,7 @@
         <v>29</v>
       </c>
       <c r="T60" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -6975,7 +6279,7 @@
         <v>46309</v>
       </c>
       <c r="N61" s="18">
-        <f>M61-L61</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="O61" s="15">
@@ -7038,7 +6342,7 @@
         <v>46309</v>
       </c>
       <c r="N62" s="18">
-        <f>M62-L62</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="O62" s="15">
@@ -7101,7 +6405,7 @@
         <v>46309</v>
       </c>
       <c r="N63" s="18">
-        <f>M63-L63</f>
+        <f t="shared" si="2"/>
         <v>52</v>
       </c>
       <c r="O63" s="15">
@@ -7164,7 +6468,7 @@
         <v>46309</v>
       </c>
       <c r="N64" s="18">
-        <f>M64-L64</f>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="O64" s="15">
@@ -7183,7 +6487,7 @@
         <v>29</v>
       </c>
       <c r="T64" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -7227,7 +6531,7 @@
         <v>46309</v>
       </c>
       <c r="N65" s="18">
-        <f>M65-L65</f>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="O65" s="15">
@@ -7246,7 +6550,7 @@
         <v>29</v>
       </c>
       <c r="T65" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -7290,7 +6594,7 @@
         <v>46309</v>
       </c>
       <c r="N66" s="18">
-        <f>M66-L66</f>
+        <f t="shared" ref="N66:N97" si="3">M66-L66</f>
         <v>46</v>
       </c>
       <c r="O66" s="15">
@@ -7309,7 +6613,7 @@
         <v>29</v>
       </c>
       <c r="T66" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -7354,7 +6658,7 @@
         <v>46309</v>
       </c>
       <c r="N67" s="18">
-        <f>M67-L67</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="O67" s="15">
@@ -7418,7 +6722,7 @@
         <v>46309</v>
       </c>
       <c r="N68" s="18">
-        <f>M68-L68</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="O68" s="15">
@@ -7436,8 +6740,8 @@
       <c r="S68" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T68" s="19" t="s">
-        <v>92</v>
+      <c r="T68" s="21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -7481,7 +6785,7 @@
         <v>46309</v>
       </c>
       <c r="N69" s="18">
-        <f>M69-L69</f>
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
       <c r="O69" s="11">
@@ -7544,7 +6848,7 @@
         <v>46309</v>
       </c>
       <c r="N70" s="18">
-        <f>M70-L70</f>
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O70" s="15">
@@ -7607,7 +6911,7 @@
         <v>46309</v>
       </c>
       <c r="N71" s="18">
-        <f>M71-L71</f>
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O71" s="15">
@@ -7670,7 +6974,7 @@
         <v>46309</v>
       </c>
       <c r="N72" s="18">
-        <f>M72-L72</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="O72" s="11">
@@ -7733,7 +7037,7 @@
         <v>46309</v>
       </c>
       <c r="N73" s="18">
-        <f>M73-L73</f>
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="O73" s="15">
@@ -7796,7 +7100,7 @@
         <v>46309</v>
       </c>
       <c r="N74" s="18">
-        <f>M74-L74</f>
+        <f t="shared" si="3"/>
         <v>77</v>
       </c>
       <c r="O74" s="11">
@@ -7859,7 +7163,7 @@
         <v>46309</v>
       </c>
       <c r="N75" s="18">
-        <f>M75-L75</f>
+        <f t="shared" si="3"/>
         <v>152</v>
       </c>
       <c r="O75" s="15">
@@ -7922,7 +7226,7 @@
         <v>46309</v>
       </c>
       <c r="N76" s="18">
-        <f>M76-L76</f>
+        <f t="shared" si="3"/>
         <v>122</v>
       </c>
       <c r="O76" s="15">
@@ -7985,7 +7289,7 @@
         <v>46309</v>
       </c>
       <c r="N77" s="18">
-        <f>M77-L77</f>
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
       <c r="O77" s="11">
@@ -8048,7 +7352,7 @@
         <v>46309</v>
       </c>
       <c r="N78" s="18">
-        <f>M78-L78</f>
+        <f t="shared" si="3"/>
         <v>180</v>
       </c>
       <c r="O78" s="15">
@@ -8112,7 +7416,7 @@
         <v>46309</v>
       </c>
       <c r="N79" s="18">
-        <f>M79-L79</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="O79" s="15">
@@ -8175,7 +7479,7 @@
         <v>46309</v>
       </c>
       <c r="N80" s="18">
-        <f>M80-L80</f>
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O80" s="15">
@@ -8238,7 +7542,7 @@
         <v>46309</v>
       </c>
       <c r="N81" s="18">
-        <f>M81-L81</f>
+        <f t="shared" si="3"/>
         <v>166</v>
       </c>
       <c r="O81" s="15">
@@ -8302,7 +7606,7 @@
         <v>46309</v>
       </c>
       <c r="N82" s="18">
-        <f>M82-L82</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="O82" s="15">
@@ -8365,7 +7669,7 @@
         <v>46309</v>
       </c>
       <c r="N83" s="18">
-        <f>M83-L83</f>
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="O83" s="15">
@@ -8429,7 +7733,7 @@
         <v>46309</v>
       </c>
       <c r="N84" s="18">
-        <f>M84-L84</f>
+        <f t="shared" si="3"/>
         <v>143</v>
       </c>
       <c r="O84" s="15">
@@ -8444,8 +7748,8 @@
       <c r="R84" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S84" s="19" t="s">
-        <v>236</v>
+      <c r="S84" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="T84" s="19" t="s">
         <v>92</v>
@@ -8492,7 +7796,7 @@
         <v>46309</v>
       </c>
       <c r="N85" s="18">
-        <f>M85-L85</f>
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="O85" s="11">
@@ -8555,7 +7859,7 @@
         <v>46309</v>
       </c>
       <c r="N86" s="18">
-        <f>M86-L86</f>
+        <f t="shared" si="3"/>
         <v>108</v>
       </c>
       <c r="O86" s="15">
@@ -8618,7 +7922,7 @@
         <v>46309</v>
       </c>
       <c r="N87" s="18">
-        <f>M87-L87</f>
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="O87" s="11">
@@ -8681,7 +7985,7 @@
         <v>46309</v>
       </c>
       <c r="N88" s="18">
-        <f>M88-L88</f>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="O88" s="15">
@@ -8745,7 +8049,7 @@
         <v>46309</v>
       </c>
       <c r="N89" s="18">
-        <f>M89-L89</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="O89" s="15">
@@ -8760,8 +8064,8 @@
       <c r="R89" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="S89" s="19" t="s">
-        <v>29</v>
+      <c r="S89" s="21" t="s">
+        <v>236</v>
       </c>
       <c r="T89" s="19" t="s">
         <v>92</v>
@@ -8809,7 +8113,7 @@
         <v>46309</v>
       </c>
       <c r="N90" s="18">
-        <f>M90-L90</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="O90" s="15">
@@ -8872,7 +8176,7 @@
         <v>46309</v>
       </c>
       <c r="N91" s="18">
-        <f>M91-L91</f>
+        <f t="shared" si="3"/>
         <v>101</v>
       </c>
       <c r="O91" s="15">
@@ -8896,120 +8200,120 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T91">
-    <sortCondition sortBy="cellColor" ref="E2:E91" dxfId="75"/>
+    <sortCondition sortBy="cellColor" ref="E2:E91" dxfId="43"/>
   </sortState>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15:E43">
+    <cfRule type="duplicateValues" dxfId="41" priority="199"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15:E49">
+    <cfRule type="duplicateValues" dxfId="40" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="200"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15:E57">
+    <cfRule type="duplicateValues" dxfId="38" priority="204"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15:E60">
+    <cfRule type="duplicateValues" dxfId="37" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="223"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E44:E45">
-    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46:E47">
-    <cfRule type="duplicateValues" dxfId="42" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:E49">
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E50:E51">
-    <cfRule type="duplicateValues" dxfId="40" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E52:E55">
-    <cfRule type="duplicateValues" dxfId="39" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E57">
-    <cfRule type="duplicateValues" dxfId="37" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="36" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E59">
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60">
+    <cfRule type="duplicateValues" dxfId="26" priority="219"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61:E67">
+    <cfRule type="duplicateValues" dxfId="25" priority="257"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61:E70">
+    <cfRule type="duplicateValues" dxfId="24" priority="259"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61:E89">
+    <cfRule type="duplicateValues" dxfId="23" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E68">
-    <cfRule type="duplicateValues" dxfId="34" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:E70">
-    <cfRule type="duplicateValues" dxfId="33" priority="24" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="25" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E71:E73">
+    <cfRule type="duplicateValues" dxfId="19" priority="270" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E74:E77">
+    <cfRule type="duplicateValues" dxfId="18" priority="262" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E78:E79">
-    <cfRule type="duplicateValues" dxfId="31" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E80:E83">
+    <cfRule type="duplicateValues" dxfId="16" priority="299" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="300" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E84:E86">
+    <cfRule type="duplicateValues" dxfId="14" priority="303" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="304" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E87:E89">
-    <cfRule type="duplicateValues" dxfId="30" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E90">
-    <cfRule type="duplicateValues" dxfId="28" priority="4" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E91">
-    <cfRule type="duplicateValues" dxfId="26" priority="2" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H69:H70">
-    <cfRule type="duplicateValues" dxfId="24" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="23" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H71:H73">
+    <cfRule type="duplicateValues" dxfId="5" priority="271" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H74:H77">
+    <cfRule type="duplicateValues" dxfId="4" priority="264" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H78:H79">
-    <cfRule type="duplicateValues" dxfId="23" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="16" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H80:H83">
+    <cfRule type="duplicateValues" dxfId="2" priority="301" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H84:H86">
+    <cfRule type="duplicateValues" dxfId="1" priority="305" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H87:H89">
-    <cfRule type="duplicateValues" dxfId="22" priority="8" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E43">
-    <cfRule type="duplicateValues" dxfId="20" priority="199"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E49">
-    <cfRule type="duplicateValues" dxfId="19" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="201"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E57">
-    <cfRule type="duplicateValues" dxfId="17" priority="204"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E60">
-    <cfRule type="duplicateValues" dxfId="16" priority="219"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E60">
-    <cfRule type="duplicateValues" dxfId="15" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="224"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E61:E67">
-    <cfRule type="duplicateValues" dxfId="13" priority="257"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E61:E70">
-    <cfRule type="duplicateValues" dxfId="12" priority="259"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E74:E77">
-    <cfRule type="duplicateValues" dxfId="11" priority="262" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H74:H77">
-    <cfRule type="duplicateValues" dxfId="10" priority="264" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E71:E73">
-    <cfRule type="duplicateValues" dxfId="9" priority="270" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H71:H73">
-    <cfRule type="duplicateValues" dxfId="8" priority="271" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E80:E83">
-    <cfRule type="duplicateValues" dxfId="7" priority="299" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="300" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H80:H83">
-    <cfRule type="duplicateValues" dxfId="5" priority="301" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E84:E86">
-    <cfRule type="duplicateValues" dxfId="4" priority="303" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="304" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H84:H86">
-    <cfRule type="duplicateValues" dxfId="2" priority="305" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E61:E89">
-    <cfRule type="duplicateValues" dxfId="1" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/UNPAID AND OVERDUE CREDIT SALES - BIKES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="411" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8C17EEB-0367-4548-AA22-F0226329A56F}"/>
+  <xr:revisionPtr revIDLastSave="430" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633FEB9B-A615-4447-B9AA-9AA041AB194D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1523,12 +1523,19 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1628,49 +1635,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1678,17 +1670,35 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2567,7 +2577,7 @@
         <v>40</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -2819,8 +2829,8 @@
       <c r="S6" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="19" t="s">
-        <v>92</v>
+      <c r="T6" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -2883,8 +2893,8 @@
       <c r="S7" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="T7" s="19" t="s">
-        <v>92</v>
+      <c r="T7" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -3070,10 +3080,10 @@
         <v>39</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -4590,8 +4600,8 @@
       <c r="S34" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="T34" s="19" t="s">
-        <v>92</v>
+      <c r="T34" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -4654,8 +4664,8 @@
       <c r="S35" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="T35" s="19" t="s">
-        <v>92</v>
+      <c r="T35" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -6046,7 +6056,7 @@
         <v>29</v>
       </c>
       <c r="T57" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -6172,7 +6182,7 @@
         <v>29</v>
       </c>
       <c r="T59" s="16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -6594,7 +6604,7 @@
         <v>46309</v>
       </c>
       <c r="N66" s="18">
-        <f t="shared" ref="N66:N97" si="3">M66-L66</f>
+        <f t="shared" ref="N66:N91" si="3">M66-L66</f>
         <v>46</v>
       </c>
       <c r="O66" s="15">
@@ -6676,8 +6686,8 @@
       <c r="S67" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T67" s="19" t="s">
-        <v>92</v>
+      <c r="T67" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -7434,8 +7444,8 @@
       <c r="S79" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T79" s="19" t="s">
-        <v>92</v>
+      <c r="T79" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -8067,8 +8077,8 @@
       <c r="S89" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="T89" s="19" t="s">
-        <v>92</v>
+      <c r="T89" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -8316,5 +8326,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/undapid and overdue credit sales -bike.xlsx
+++ b/undapid and overdue credit sales -bike.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/UNPAID AND OVERDUE CREDIT SALES - BIKES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="430" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633FEB9B-A615-4447-B9AA-9AA041AB194D}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="11_C05646ABB6493BA2E9AD59851B29C1BC842019F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55F38762-BF39-476C-B41B-2EB1046BBC15}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2438,16 +2438,16 @@
     <col min="4" max="4" width="15.90625" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="40" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="6.54296875" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="9.36328125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1796875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="13.453125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" customWidth="1"/>
+    <col min="11" max="11" width="6.54296875" customWidth="1"/>
+    <col min="12" max="12" width="9.36328125" customWidth="1"/>
+    <col min="13" max="13" width="9.7265625" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
+    <col min="16" max="16" width="13.7265625" customWidth="1"/>
     <col min="17" max="17" width="40.1796875" customWidth="1"/>
     <col min="18" max="18" width="38.08984375" customWidth="1"/>
     <col min="19" max="19" width="27.6328125" bestFit="1" customWidth="1"/>
